--- a/reports/CD_OUTAGE_23072026.xlsx
+++ b/reports/CD_OUTAGE_23072026.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy hh:mm"/>
-    <numFmt numFmtId="166" formatCode="[h]:mm"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy hh:mm"/>
+    <numFmt numFmtId="165" formatCode="[h]:mm"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -59,11 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,10 +524,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 3 (2G)(4G) xC sites at certain parts of Kajang / Sg Chua area, Selangor</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>46226.85</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="5">
         <f>IF(AND(E2&lt;&gt;"",F2&lt;&gt;""),F2-E2,"")</f>
         <v/>
       </c>
@@ -562,10 +563,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 3 (2G)(4G) xC sites at certain parts of Kajang / Sg Chua area, Selangor</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>46226.85</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="5">
         <f>IF(AND(E3&lt;&gt;"",F3&lt;&gt;""),F3-E3,"")</f>
         <v/>
       </c>
@@ -601,10 +602,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 3 (2G)(4G) xC sites at certain parts of Kajang / Sg Chua area, Selangor</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4" t="n">
         <v>46226.85</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="5">
         <f>IF(AND(E4&lt;&gt;"",F4&lt;&gt;""),F4-E4,"")</f>
         <v/>
       </c>
@@ -640,10 +641,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 3 (2G)(4G) xC sites at certain parts of Kajang / Sg Chua area, Selangor</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>46226.85</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="5">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),F5-E5,"")</f>
         <v/>
       </c>
@@ -679,10 +680,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 3 (2G)(4G) xC sites at certain parts of Kajang / Sg Chua area, Selangor</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>46226.85</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="5">
         <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),F6-E6,"")</f>
         <v/>
       </c>
@@ -718,10 +719,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 3 (2G)(4G) xC sites at certain parts of Kajang / Sg Chua area, Selangor</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>46226.85</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="5">
         <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),F7-E7,"")</f>
         <v/>
       </c>
@@ -757,10 +758,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan area, Sabah</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>46226.83194444444</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="5">
         <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),F8-E8,"")</f>
         <v/>
       </c>
@@ -796,10 +797,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan area, Sabah</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>46226.83194444444</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="5">
         <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),F9-E9,"")</f>
         <v/>
       </c>
@@ -835,10 +836,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan area, Sabah</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="4" t="n">
         <v>46226.83194444444</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="5">
         <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),F10-E10,"")</f>
         <v/>
       </c>
@@ -874,10 +875,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan area, Sabah</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="4" t="n">
         <v>46226.83194444444</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="5">
         <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),F11-E11,"")</f>
         <v/>
       </c>
@@ -913,10 +914,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan area, Sabah</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="4" t="n">
         <v>46226.83194444444</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="5">
         <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),F12-E12,"")</f>
         <v/>
       </c>
@@ -952,10 +953,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Lahad Datu-Kinabatangan area, Sabah</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="4" t="n">
         <v>46226.83194444444</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="5">
         <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),F13-E13,"")</f>
         <v/>
       </c>
@@ -991,10 +992,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="4" t="n">
         <v>46226.81180555555</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="5">
         <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),F14-E14,"")</f>
         <v/>
       </c>
@@ -1030,10 +1031,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="4" t="n">
         <v>46226.81180555555</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="5">
         <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),F15-E15,"")</f>
         <v/>
       </c>
@@ -1069,10 +1070,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="4" t="n">
         <v>46226.81180555555</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="5">
         <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),F16-E16,"")</f>
         <v/>
       </c>
@@ -1108,10 +1109,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="4" t="n">
         <v>46226.81180555555</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="5">
         <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),F17-E17,"")</f>
         <v/>
       </c>
@@ -1147,10 +1148,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="4" t="n">
         <v>46226.81180555555</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="5">
         <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),F18-E18,"")</f>
         <v/>
       </c>
@@ -1186,10 +1187,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi, Mile 2 To 9 area, Sarawak</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="4" t="n">
         <v>46226.77916666667</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="5">
         <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),F19-E19,"")</f>
         <v/>
       </c>
@@ -1225,10 +1226,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi, Mile 2 To 9 area, Sarawak</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="4" t="n">
         <v>46226.77916666667</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="5">
         <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),F20-E20,"")</f>
         <v/>
       </c>
@@ -1264,10 +1265,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi, Mile 2 To 9 area, Sarawak</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="4" t="n">
         <v>46226.77916666667</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="5">
         <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),F21-E21,"")</f>
         <v/>
       </c>
@@ -1303,10 +1304,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi, Mile 2 To 9 area, Sarawak</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="4" t="n">
         <v>46226.77916666667</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="5">
         <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),F22-E22,"")</f>
         <v/>
       </c>
@@ -1342,10 +1343,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi, Mile 2 To 9 area, Sarawak</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="4" t="n">
         <v>46226.77916666667</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="5">
         <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),F23-E23,"")</f>
         <v/>
       </c>
@@ -1376,10 +1377,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi, Mile 2 To 9 area, Sarawak</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="4" t="n">
         <v>46226.77916666667</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="5">
         <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),F24-E24,"")</f>
         <v/>
       </c>
@@ -1410,10 +1411,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi, Mile 2 To 9 area, Sarawak</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="4" t="n">
         <v>46226.77916666667</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="5">
         <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),F25-E25,"")</f>
         <v/>
       </c>
@@ -1444,10 +1445,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi, Mile 2 To 9 area, Sarawak</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="4" t="n">
         <v>46226.77916666667</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="5">
         <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),F26-E26,"")</f>
         <v/>
       </c>
@@ -1483,10 +1484,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bekenu / Batu Niah / Marudi, Mile 2 To 9 area, Sarawak</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="4" t="n">
         <v>46226.77916666667</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="5">
         <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),F27-E27,"")</f>
         <v/>
       </c>
@@ -1522,13 +1523,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F28" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="5">
         <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),F28-E28,"")</f>
         <v/>
       </c>
@@ -1574,13 +1575,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="F29" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="5">
         <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),F29-E29,"")</f>
         <v/>
       </c>
@@ -1626,13 +1627,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="F30" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="5">
         <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),F30-E30,"")</f>
         <v/>
       </c>
@@ -1673,13 +1674,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="F31" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="5">
         <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),F31-E31,"")</f>
         <v/>
       </c>
@@ -1725,13 +1726,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="F32" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="5">
         <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),F32-E32,"")</f>
         <v/>
       </c>
@@ -1777,13 +1778,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="F33" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="5">
         <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),F33-E33,"")</f>
         <v/>
       </c>
@@ -1829,13 +1830,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F34" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="5">
         <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),F34-E34,"")</f>
         <v/>
       </c>
@@ -1881,13 +1882,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="F35" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="5">
         <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),F35-E35,"")</f>
         <v/>
       </c>
@@ -1933,13 +1934,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="F36" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="5">
         <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),F36-E36,"")</f>
         <v/>
       </c>
@@ -1985,13 +1986,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="F37" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="5">
         <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),F37-E37,"")</f>
         <v/>
       </c>
@@ -2037,13 +2038,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="F38" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="5">
         <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),F38-E38,"")</f>
         <v/>
       </c>
@@ -2089,13 +2090,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="F39" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="5">
         <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),F39-E39,"")</f>
         <v/>
       </c>
@@ -2141,13 +2142,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="F40" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="5">
         <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),F40-E40,"")</f>
         <v/>
       </c>
@@ -2193,13 +2194,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="F41" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="5">
         <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),F41-E41,"")</f>
         <v/>
       </c>
@@ -2245,13 +2246,13 @@
           <t>Service interruption of 13 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Sarikei / Kanowit 1, Kunak area, Sarawak, Sabah</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="4" t="n">
         <v>46226.76319444444</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="F42" s="4" t="n">
         <v>46226.78888888889</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="5">
         <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),F42-E42,"")</f>
         <v/>
       </c>
@@ -2297,10 +2298,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="5">
         <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),F43-E43,"")</f>
         <v/>
       </c>
@@ -2336,10 +2337,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="5">
         <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),F44-E44,"")</f>
         <v/>
       </c>
@@ -2375,10 +2376,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="5">
         <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),F45-E45,"")</f>
         <v/>
       </c>
@@ -2414,10 +2415,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="5">
         <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),F46-E46,"")</f>
         <v/>
       </c>
@@ -2453,10 +2454,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="5">
         <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),F47-E47,"")</f>
         <v/>
       </c>
@@ -2492,10 +2493,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="5">
         <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),F48-E48,"")</f>
         <v/>
       </c>
@@ -2531,10 +2532,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="5">
         <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),F49-E49,"")</f>
         <v/>
       </c>
@@ -2570,10 +2571,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="5">
         <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),F50-E50,"")</f>
         <v/>
       </c>
@@ -2604,10 +2605,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="5">
         <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),F51-E51,"")</f>
         <v/>
       </c>
@@ -2643,10 +2644,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E52" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="5">
         <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),F52-E52,"")</f>
         <v/>
       </c>
@@ -2682,10 +2683,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="5">
         <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),F53-E53,"")</f>
         <v/>
       </c>
@@ -2716,10 +2717,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 8 (2G)(4G) xC sites at certain parts of Bentong, Raub area, Pahang</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="4" t="n">
         <v>46226.76111111111</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="5">
         <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),F54-E54,"")</f>
         <v/>
       </c>
@@ -2755,10 +2756,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="5">
         <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),F55-E55,"")</f>
         <v/>
       </c>
@@ -2794,10 +2795,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="5">
         <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),F56-E56,"")</f>
         <v/>
       </c>
@@ -2833,10 +2834,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="5">
         <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),F57-E57,"")</f>
         <v/>
       </c>
@@ -2867,10 +2868,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E58" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="5">
         <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),F58-E58,"")</f>
         <v/>
       </c>
@@ -2901,10 +2902,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="5">
         <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),F59-E59,"")</f>
         <v/>
       </c>
@@ -2940,10 +2941,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E60" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60" s="5">
         <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),F60-E60,"")</f>
         <v/>
       </c>
@@ -2979,10 +2980,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E61" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61" s="5">
         <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),F61-E61,"")</f>
         <v/>
       </c>
@@ -3013,10 +3014,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="5">
         <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),F62-E62,"")</f>
         <v/>
       </c>
@@ -3052,10 +3053,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E63" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G63" s="5">
         <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),F63-E63,"")</f>
         <v/>
       </c>
@@ -3091,10 +3092,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G64" s="5">
         <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),F64-E64,"")</f>
         <v/>
       </c>
@@ -3130,10 +3131,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G65" s="5">
         <f>IF(AND(E65&lt;&gt;"",F65&lt;&gt;""),F65-E65,"")</f>
         <v/>
       </c>
@@ -3169,10 +3170,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E66" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G66" s="5">
         <f>IF(AND(E66&lt;&gt;"",F66&lt;&gt;""),F66-E66,"")</f>
         <v/>
       </c>
@@ -3208,10 +3209,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G67" s="5">
         <f>IF(AND(E67&lt;&gt;"",F67&lt;&gt;""),F67-E67,"")</f>
         <v/>
       </c>
@@ -3242,10 +3243,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G68" s="5">
         <f>IF(AND(E68&lt;&gt;"",F68&lt;&gt;""),F68-E68,"")</f>
         <v/>
       </c>
@@ -3281,10 +3282,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G69" s="3">
+      <c r="G69" s="5">
         <f>IF(AND(E69&lt;&gt;"",F69&lt;&gt;""),F69-E69,"")</f>
         <v/>
       </c>
@@ -3315,10 +3316,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E70" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G70" s="3">
+      <c r="G70" s="5">
         <f>IF(AND(E70&lt;&gt;"",F70&lt;&gt;""),F70-E70,"")</f>
         <v/>
       </c>
@@ -3354,10 +3355,10 @@
           <t>Service interruption of 11 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Kapit, Mukah / Matu Daro, Sibu 6 area, Sarawak</t>
         </is>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" s="4" t="n">
         <v>46226.67569444444</v>
       </c>
-      <c r="G71" s="3">
+      <c r="G71" s="5">
         <f>IF(AND(E71&lt;&gt;"",F71&lt;&gt;""),F71-E71,"")</f>
         <v/>
       </c>
@@ -3393,13 +3394,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E72" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F72" s="2" t="n">
+      <c r="F72" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="5">
         <f>IF(AND(E72&lt;&gt;"",F72&lt;&gt;""),F72-E72,"")</f>
         <v/>
       </c>
@@ -3445,13 +3446,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="F73" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G73" s="5">
         <f>IF(AND(E73&lt;&gt;"",F73&lt;&gt;""),F73-E73,"")</f>
         <v/>
       </c>
@@ -3497,13 +3498,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E74" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="F74" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G74" s="3">
+      <c r="G74" s="5">
         <f>IF(AND(E74&lt;&gt;"",F74&lt;&gt;""),F74-E74,"")</f>
         <v/>
       </c>
@@ -3549,13 +3550,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E75" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="F75" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75" s="5">
         <f>IF(AND(E75&lt;&gt;"",F75&lt;&gt;""),F75-E75,"")</f>
         <v/>
       </c>
@@ -3601,13 +3602,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="F76" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G76" s="5">
         <f>IF(AND(E76&lt;&gt;"",F76&lt;&gt;""),F76-E76,"")</f>
         <v/>
       </c>
@@ -3653,13 +3654,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E77" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="F77" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G77" s="5">
         <f>IF(AND(E77&lt;&gt;"",F77&lt;&gt;""),F77-E77,"")</f>
         <v/>
       </c>
@@ -3705,13 +3706,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E78" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="F78" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G78" s="3">
+      <c r="G78" s="5">
         <f>IF(AND(E78&lt;&gt;"",F78&lt;&gt;""),F78-E78,"")</f>
         <v/>
       </c>
@@ -3757,13 +3758,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E79" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="F79" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G79" s="5">
         <f>IF(AND(E79&lt;&gt;"",F79&lt;&gt;""),F79-E79,"")</f>
         <v/>
       </c>
@@ -3809,13 +3810,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="E80" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="F80" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G80" s="3">
+      <c r="G80" s="5">
         <f>IF(AND(E80&lt;&gt;"",F80&lt;&gt;""),F80-E80,"")</f>
         <v/>
       </c>
@@ -3861,13 +3862,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E81" s="2" t="n">
+      <c r="E81" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="F81" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G81" s="3">
+      <c r="G81" s="5">
         <f>IF(AND(E81&lt;&gt;"",F81&lt;&gt;""),F81-E81,"")</f>
         <v/>
       </c>
@@ -3913,13 +3914,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="E82" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="F82" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G82" s="3">
+      <c r="G82" s="5">
         <f>IF(AND(E82&lt;&gt;"",F82&lt;&gt;""),F82-E82,"")</f>
         <v/>
       </c>
@@ -3965,13 +3966,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E83" s="2" t="n">
+      <c r="E83" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="F83" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="5">
         <f>IF(AND(E83&lt;&gt;"",F83&lt;&gt;""),F83-E83,"")</f>
         <v/>
       </c>
@@ -4017,13 +4018,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E84" s="2" t="n">
+      <c r="E84" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="F84" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G84" s="3">
+      <c r="G84" s="5">
         <f>IF(AND(E84&lt;&gt;"",F84&lt;&gt;""),F84-E84,"")</f>
         <v/>
       </c>
@@ -4069,13 +4070,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E85" s="2" t="n">
+      <c r="E85" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="F85" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G85" s="3">
+      <c r="G85" s="5">
         <f>IF(AND(E85&lt;&gt;"",F85&lt;&gt;""),F85-E85,"")</f>
         <v/>
       </c>
@@ -4121,13 +4122,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E86" s="2" t="n">
+      <c r="E86" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="F86" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G86" s="3">
+      <c r="G86" s="5">
         <f>IF(AND(E86&lt;&gt;"",F86&lt;&gt;""),F86-E86,"")</f>
         <v/>
       </c>
@@ -4173,13 +4174,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="E87" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="F87" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G87" s="3">
+      <c r="G87" s="5">
         <f>IF(AND(E87&lt;&gt;"",F87&lt;&gt;""),F87-E87,"")</f>
         <v/>
       </c>
@@ -4225,13 +4226,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E88" s="2" t="n">
+      <c r="E88" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="F88" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G88" s="3">
+      <c r="G88" s="5">
         <f>IF(AND(E88&lt;&gt;"",F88&lt;&gt;""),F88-E88,"")</f>
         <v/>
       </c>
@@ -4277,13 +4278,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E89" s="2" t="n">
+      <c r="E89" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F89" s="2" t="n">
+      <c r="F89" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="5">
         <f>IF(AND(E89&lt;&gt;"",F89&lt;&gt;""),F89-E89,"")</f>
         <v/>
       </c>
@@ -4329,13 +4330,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E90" s="2" t="n">
+      <c r="E90" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F90" s="2" t="n">
+      <c r="F90" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G90" s="3">
+      <c r="G90" s="5">
         <f>IF(AND(E90&lt;&gt;"",F90&lt;&gt;""),F90-E90,"")</f>
         <v/>
       </c>
@@ -4381,13 +4382,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="E91" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="F91" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="5">
         <f>IF(AND(E91&lt;&gt;"",F91&lt;&gt;""),F91-E91,"")</f>
         <v/>
       </c>
@@ -4433,13 +4434,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E92" s="2" t="n">
+      <c r="E92" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F92" s="2" t="n">
+      <c r="F92" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G92" s="3">
+      <c r="G92" s="5">
         <f>IF(AND(E92&lt;&gt;"",F92&lt;&gt;""),F92-E92,"")</f>
         <v/>
       </c>
@@ -4485,13 +4486,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E93" s="2" t="n">
+      <c r="E93" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F93" s="2" t="n">
+      <c r="F93" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G93" s="3">
+      <c r="G93" s="5">
         <f>IF(AND(E93&lt;&gt;"",F93&lt;&gt;""),F93-E93,"")</f>
         <v/>
       </c>
@@ -4537,13 +4538,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E94" s="2" t="n">
+      <c r="E94" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F94" s="2" t="n">
+      <c r="F94" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="5">
         <f>IF(AND(E94&lt;&gt;"",F94&lt;&gt;""),F94-E94,"")</f>
         <v/>
       </c>
@@ -4589,13 +4590,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E95" s="2" t="n">
+      <c r="E95" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F95" s="2" t="n">
+      <c r="F95" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G95" s="3">
+      <c r="G95" s="5">
         <f>IF(AND(E95&lt;&gt;"",F95&lt;&gt;""),F95-E95,"")</f>
         <v/>
       </c>
@@ -4641,13 +4642,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E96" s="2" t="n">
+      <c r="E96" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F96" s="2" t="n">
+      <c r="F96" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96" s="5">
         <f>IF(AND(E96&lt;&gt;"",F96&lt;&gt;""),F96-E96,"")</f>
         <v/>
       </c>
@@ -4693,13 +4694,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E97" s="2" t="n">
+      <c r="E97" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F97" s="2" t="n">
+      <c r="F97" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G97" s="3">
+      <c r="G97" s="5">
         <f>IF(AND(E97&lt;&gt;"",F97&lt;&gt;""),F97-E97,"")</f>
         <v/>
       </c>
@@ -4745,13 +4746,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E98" s="2" t="n">
+      <c r="E98" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F98" s="2" t="n">
+      <c r="F98" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G98" s="3">
+      <c r="G98" s="5">
         <f>IF(AND(E98&lt;&gt;"",F98&lt;&gt;""),F98-E98,"")</f>
         <v/>
       </c>
@@ -4797,13 +4798,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E99" s="2" t="n">
+      <c r="E99" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F99" s="2" t="n">
+      <c r="F99" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G99" s="3">
+      <c r="G99" s="5">
         <f>IF(AND(E99&lt;&gt;"",F99&lt;&gt;""),F99-E99,"")</f>
         <v/>
       </c>
@@ -4849,13 +4850,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E100" s="2" t="n">
+      <c r="E100" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F100" s="2" t="n">
+      <c r="F100" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="5">
         <f>IF(AND(E100&lt;&gt;"",F100&lt;&gt;""),F100-E100,"")</f>
         <v/>
       </c>
@@ -4901,13 +4902,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E101" s="2" t="n">
+      <c r="E101" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F101" s="2" t="n">
+      <c r="F101" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="5">
         <f>IF(AND(E101&lt;&gt;"",F101&lt;&gt;""),F101-E101,"")</f>
         <v/>
       </c>
@@ -4953,13 +4954,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E102" s="2" t="n">
+      <c r="E102" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F102" s="2" t="n">
+      <c r="F102" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G102" s="5">
         <f>IF(AND(E102&lt;&gt;"",F102&lt;&gt;""),F102-E102,"")</f>
         <v/>
       </c>
@@ -5005,13 +5006,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="E103" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F103" s="2" t="n">
+      <c r="F103" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G103" s="3">
+      <c r="G103" s="5">
         <f>IF(AND(E103&lt;&gt;"",F103&lt;&gt;""),F103-E103,"")</f>
         <v/>
       </c>
@@ -5057,13 +5058,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E104" s="2" t="n">
+      <c r="E104" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F104" s="2" t="n">
+      <c r="F104" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G104" s="5">
         <f>IF(AND(E104&lt;&gt;"",F104&lt;&gt;""),F104-E104,"")</f>
         <v/>
       </c>
@@ -5109,13 +5110,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E105" s="2" t="n">
+      <c r="E105" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F105" s="2" t="n">
+      <c r="F105" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G105" s="3">
+      <c r="G105" s="5">
         <f>IF(AND(E105&lt;&gt;"",F105&lt;&gt;""),F105-E105,"")</f>
         <v/>
       </c>
@@ -5161,13 +5162,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E106" s="2" t="n">
+      <c r="E106" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F106" s="2" t="n">
+      <c r="F106" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G106" s="3">
+      <c r="G106" s="5">
         <f>IF(AND(E106&lt;&gt;"",F106&lt;&gt;""),F106-E106,"")</f>
         <v/>
       </c>
@@ -5213,13 +5214,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E107" s="2" t="n">
+      <c r="E107" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F107" s="2" t="n">
+      <c r="F107" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G107" s="3">
+      <c r="G107" s="5">
         <f>IF(AND(E107&lt;&gt;"",F107&lt;&gt;""),F107-E107,"")</f>
         <v/>
       </c>
@@ -5265,13 +5266,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E108" s="2" t="n">
+      <c r="E108" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F108" s="2" t="n">
+      <c r="F108" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G108" s="3">
+      <c r="G108" s="5">
         <f>IF(AND(E108&lt;&gt;"",F108&lt;&gt;""),F108-E108,"")</f>
         <v/>
       </c>
@@ -5317,13 +5318,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E109" s="2" t="n">
+      <c r="E109" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F109" s="2" t="n">
+      <c r="F109" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G109" s="3">
+      <c r="G109" s="5">
         <f>IF(AND(E109&lt;&gt;"",F109&lt;&gt;""),F109-E109,"")</f>
         <v/>
       </c>
@@ -5369,13 +5370,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E110" s="2" t="n">
+      <c r="E110" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F110" s="2" t="n">
+      <c r="F110" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G110" s="3">
+      <c r="G110" s="5">
         <f>IF(AND(E110&lt;&gt;"",F110&lt;&gt;""),F110-E110,"")</f>
         <v/>
       </c>
@@ -5421,13 +5422,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E111" s="2" t="n">
+      <c r="E111" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F111" s="2" t="n">
+      <c r="F111" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G111" s="3">
+      <c r="G111" s="5">
         <f>IF(AND(E111&lt;&gt;"",F111&lt;&gt;""),F111-E111,"")</f>
         <v/>
       </c>
@@ -5473,13 +5474,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E112" s="2" t="n">
+      <c r="E112" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F112" s="2" t="n">
+      <c r="F112" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G112" s="3">
+      <c r="G112" s="5">
         <f>IF(AND(E112&lt;&gt;"",F112&lt;&gt;""),F112-E112,"")</f>
         <v/>
       </c>
@@ -5525,13 +5526,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E113" s="2" t="n">
+      <c r="E113" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F113" s="2" t="n">
+      <c r="F113" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G113" s="3">
+      <c r="G113" s="5">
         <f>IF(AND(E113&lt;&gt;"",F113&lt;&gt;""),F113-E113,"")</f>
         <v/>
       </c>
@@ -5577,13 +5578,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E114" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F114" s="2" t="n">
+      <c r="F114" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G114" s="3">
+      <c r="G114" s="5">
         <f>IF(AND(E114&lt;&gt;"",F114&lt;&gt;""),F114-E114,"")</f>
         <v/>
       </c>
@@ -5629,13 +5630,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E115" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F115" s="2" t="n">
+      <c r="F115" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G115" s="3">
+      <c r="G115" s="5">
         <f>IF(AND(E115&lt;&gt;"",F115&lt;&gt;""),F115-E115,"")</f>
         <v/>
       </c>
@@ -5681,13 +5682,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E116" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F116" s="2" t="n">
+      <c r="F116" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G116" s="3">
+      <c r="G116" s="5">
         <f>IF(AND(E116&lt;&gt;"",F116&lt;&gt;""),F116-E116,"")</f>
         <v/>
       </c>
@@ -5733,13 +5734,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E117" s="2" t="n">
+      <c r="E117" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F117" s="2" t="n">
+      <c r="F117" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G117" s="3">
+      <c r="G117" s="5">
         <f>IF(AND(E117&lt;&gt;"",F117&lt;&gt;""),F117-E117,"")</f>
         <v/>
       </c>
@@ -5785,13 +5786,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E118" s="2" t="n">
+      <c r="E118" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F118" s="2" t="n">
+      <c r="F118" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G118" s="3">
+      <c r="G118" s="5">
         <f>IF(AND(E118&lt;&gt;"",F118&lt;&gt;""),F118-E118,"")</f>
         <v/>
       </c>
@@ -5837,13 +5838,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E119" s="2" t="n">
+      <c r="E119" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F119" s="2" t="n">
+      <c r="F119" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G119" s="3">
+      <c r="G119" s="5">
         <f>IF(AND(E119&lt;&gt;"",F119&lt;&gt;""),F119-E119,"")</f>
         <v/>
       </c>
@@ -5889,13 +5890,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E120" s="2" t="n">
+      <c r="E120" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F120" s="2" t="n">
+      <c r="F120" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G120" s="3">
+      <c r="G120" s="5">
         <f>IF(AND(E120&lt;&gt;"",F120&lt;&gt;""),F120-E120,"")</f>
         <v/>
       </c>
@@ -5941,13 +5942,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E121" s="2" t="n">
+      <c r="E121" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F121" s="2" t="n">
+      <c r="F121" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G121" s="3">
+      <c r="G121" s="5">
         <f>IF(AND(E121&lt;&gt;"",F121&lt;&gt;""),F121-E121,"")</f>
         <v/>
       </c>
@@ -5993,13 +5994,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E122" s="2" t="n">
+      <c r="E122" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F122" s="2" t="n">
+      <c r="F122" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G122" s="3">
+      <c r="G122" s="5">
         <f>IF(AND(E122&lt;&gt;"",F122&lt;&gt;""),F122-E122,"")</f>
         <v/>
       </c>
@@ -6045,13 +6046,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E123" s="2" t="n">
+      <c r="E123" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F123" s="2" t="n">
+      <c r="F123" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G123" s="3">
+      <c r="G123" s="5">
         <f>IF(AND(E123&lt;&gt;"",F123&lt;&gt;""),F123-E123,"")</f>
         <v/>
       </c>
@@ -6097,13 +6098,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E124" s="2" t="n">
+      <c r="E124" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F124" s="2" t="n">
+      <c r="F124" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G124" s="3">
+      <c r="G124" s="5">
         <f>IF(AND(E124&lt;&gt;"",F124&lt;&gt;""),F124-E124,"")</f>
         <v/>
       </c>
@@ -6149,13 +6150,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E125" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F125" s="2" t="n">
+      <c r="F125" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G125" s="3">
+      <c r="G125" s="5">
         <f>IF(AND(E125&lt;&gt;"",F125&lt;&gt;""),F125-E125,"")</f>
         <v/>
       </c>
@@ -6201,13 +6202,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E126" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F126" s="2" t="n">
+      <c r="F126" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G126" s="3">
+      <c r="G126" s="5">
         <f>IF(AND(E126&lt;&gt;"",F126&lt;&gt;""),F126-E126,"")</f>
         <v/>
       </c>
@@ -6253,13 +6254,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E127" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F127" s="2" t="n">
+      <c r="F127" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G127" s="3">
+      <c r="G127" s="5">
         <f>IF(AND(E127&lt;&gt;"",F127&lt;&gt;""),F127-E127,"")</f>
         <v/>
       </c>
@@ -6305,13 +6306,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E128" s="2" t="n">
+      <c r="E128" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F128" s="2" t="n">
+      <c r="F128" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G128" s="3">
+      <c r="G128" s="5">
         <f>IF(AND(E128&lt;&gt;"",F128&lt;&gt;""),F128-E128,"")</f>
         <v/>
       </c>
@@ -6357,13 +6358,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E129" s="2" t="n">
+      <c r="E129" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F129" s="2" t="n">
+      <c r="F129" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G129" s="3">
+      <c r="G129" s="5">
         <f>IF(AND(E129&lt;&gt;"",F129&lt;&gt;""),F129-E129,"")</f>
         <v/>
       </c>
@@ -6409,13 +6410,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E130" s="2" t="n">
+      <c r="E130" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F130" s="2" t="n">
+      <c r="F130" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G130" s="3">
+      <c r="G130" s="5">
         <f>IF(AND(E130&lt;&gt;"",F130&lt;&gt;""),F130-E130,"")</f>
         <v/>
       </c>
@@ -6461,13 +6462,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E131" s="2" t="n">
+      <c r="E131" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F131" s="2" t="n">
+      <c r="F131" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G131" s="3">
+      <c r="G131" s="5">
         <f>IF(AND(E131&lt;&gt;"",F131&lt;&gt;""),F131-E131,"")</f>
         <v/>
       </c>
@@ -6513,13 +6514,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E132" s="2" t="n">
+      <c r="E132" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F132" s="2" t="n">
+      <c r="F132" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G132" s="3">
+      <c r="G132" s="5">
         <f>IF(AND(E132&lt;&gt;"",F132&lt;&gt;""),F132-E132,"")</f>
         <v/>
       </c>
@@ -6565,13 +6566,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E133" s="2" t="n">
+      <c r="E133" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F133" s="2" t="n">
+      <c r="F133" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G133" s="3">
+      <c r="G133" s="5">
         <f>IF(AND(E133&lt;&gt;"",F133&lt;&gt;""),F133-E133,"")</f>
         <v/>
       </c>
@@ -6617,13 +6618,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E134" s="2" t="n">
+      <c r="E134" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F134" s="2" t="n">
+      <c r="F134" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G134" s="3">
+      <c r="G134" s="5">
         <f>IF(AND(E134&lt;&gt;"",F134&lt;&gt;""),F134-E134,"")</f>
         <v/>
       </c>
@@ -6669,13 +6670,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E135" s="2" t="n">
+      <c r="E135" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F135" s="2" t="n">
+      <c r="F135" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G135" s="3">
+      <c r="G135" s="5">
         <f>IF(AND(E135&lt;&gt;"",F135&lt;&gt;""),F135-E135,"")</f>
         <v/>
       </c>
@@ -6721,13 +6722,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E136" s="2" t="n">
+      <c r="E136" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F136" s="2" t="n">
+      <c r="F136" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G136" s="3">
+      <c r="G136" s="5">
         <f>IF(AND(E136&lt;&gt;"",F136&lt;&gt;""),F136-E136,"")</f>
         <v/>
       </c>
@@ -6773,13 +6774,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E137" s="2" t="n">
+      <c r="E137" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F137" s="2" t="n">
+      <c r="F137" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G137" s="3">
+      <c r="G137" s="5">
         <f>IF(AND(E137&lt;&gt;"",F137&lt;&gt;""),F137-E137,"")</f>
         <v/>
       </c>
@@ -6825,13 +6826,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E138" s="2" t="n">
+      <c r="E138" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F138" s="2" t="n">
+      <c r="F138" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G138" s="3">
+      <c r="G138" s="5">
         <f>IF(AND(E138&lt;&gt;"",F138&lt;&gt;""),F138-E138,"")</f>
         <v/>
       </c>
@@ -6877,13 +6878,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E139" s="2" t="n">
+      <c r="E139" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F139" s="2" t="n">
+      <c r="F139" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G139" s="3">
+      <c r="G139" s="5">
         <f>IF(AND(E139&lt;&gt;"",F139&lt;&gt;""),F139-E139,"")</f>
         <v/>
       </c>
@@ -6929,13 +6930,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E140" s="2" t="n">
+      <c r="E140" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F140" s="2" t="n">
+      <c r="F140" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G140" s="3">
+      <c r="G140" s="5">
         <f>IF(AND(E140&lt;&gt;"",F140&lt;&gt;""),F140-E140,"")</f>
         <v/>
       </c>
@@ -6981,13 +6982,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E141" s="2" t="n">
+      <c r="E141" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F141" s="2" t="n">
+      <c r="F141" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G141" s="3">
+      <c r="G141" s="5">
         <f>IF(AND(E141&lt;&gt;"",F141&lt;&gt;""),F141-E141,"")</f>
         <v/>
       </c>
@@ -7033,13 +7034,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E142" s="2" t="n">
+      <c r="E142" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F142" s="2" t="n">
+      <c r="F142" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G142" s="3">
+      <c r="G142" s="5">
         <f>IF(AND(E142&lt;&gt;"",F142&lt;&gt;""),F142-E142,"")</f>
         <v/>
       </c>
@@ -7085,13 +7086,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E143" s="2" t="n">
+      <c r="E143" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F143" s="2" t="n">
+      <c r="F143" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G143" s="3">
+      <c r="G143" s="5">
         <f>IF(AND(E143&lt;&gt;"",F143&lt;&gt;""),F143-E143,"")</f>
         <v/>
       </c>
@@ -7137,13 +7138,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E144" s="2" t="n">
+      <c r="E144" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F144" s="2" t="n">
+      <c r="F144" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G144" s="3">
+      <c r="G144" s="5">
         <f>IF(AND(E144&lt;&gt;"",F144&lt;&gt;""),F144-E144,"")</f>
         <v/>
       </c>
@@ -7189,13 +7190,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E145" s="2" t="n">
+      <c r="E145" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F145" s="2" t="n">
+      <c r="F145" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G145" s="3">
+      <c r="G145" s="5">
         <f>IF(AND(E145&lt;&gt;"",F145&lt;&gt;""),F145-E145,"")</f>
         <v/>
       </c>
@@ -7241,13 +7242,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E146" s="2" t="n">
+      <c r="E146" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F146" s="2" t="n">
+      <c r="F146" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G146" s="3">
+      <c r="G146" s="5">
         <f>IF(AND(E146&lt;&gt;"",F146&lt;&gt;""),F146-E146,"")</f>
         <v/>
       </c>
@@ -7293,13 +7294,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E147" s="2" t="n">
+      <c r="E147" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F147" s="2" t="n">
+      <c r="F147" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G147" s="3">
+      <c r="G147" s="5">
         <f>IF(AND(E147&lt;&gt;"",F147&lt;&gt;""),F147-E147,"")</f>
         <v/>
       </c>
@@ -7345,13 +7346,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E148" s="2" t="n">
+      <c r="E148" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F148" s="2" t="n">
+      <c r="F148" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G148" s="3">
+      <c r="G148" s="5">
         <f>IF(AND(E148&lt;&gt;"",F148&lt;&gt;""),F148-E148,"")</f>
         <v/>
       </c>
@@ -7397,13 +7398,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E149" s="2" t="n">
+      <c r="E149" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F149" s="2" t="n">
+      <c r="F149" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G149" s="3">
+      <c r="G149" s="5">
         <f>IF(AND(E149&lt;&gt;"",F149&lt;&gt;""),F149-E149,"")</f>
         <v/>
       </c>
@@ -7449,13 +7450,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E150" s="2" t="n">
+      <c r="E150" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F150" s="2" t="n">
+      <c r="F150" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G150" s="3">
+      <c r="G150" s="5">
         <f>IF(AND(E150&lt;&gt;"",F150&lt;&gt;""),F150-E150,"")</f>
         <v/>
       </c>
@@ -7501,13 +7502,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E151" s="2" t="n">
+      <c r="E151" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F151" s="2" t="n">
+      <c r="F151" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G151" s="3">
+      <c r="G151" s="5">
         <f>IF(AND(E151&lt;&gt;"",F151&lt;&gt;""),F151-E151,"")</f>
         <v/>
       </c>
@@ -7553,13 +7554,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E152" s="2" t="n">
+      <c r="E152" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F152" s="2" t="n">
+      <c r="F152" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G152" s="3">
+      <c r="G152" s="5">
         <f>IF(AND(E152&lt;&gt;"",F152&lt;&gt;""),F152-E152,"")</f>
         <v/>
       </c>
@@ -7605,13 +7606,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E153" s="2" t="n">
+      <c r="E153" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F153" s="2" t="n">
+      <c r="F153" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G153" s="3">
+      <c r="G153" s="5">
         <f>IF(AND(E153&lt;&gt;"",F153&lt;&gt;""),F153-E153,"")</f>
         <v/>
       </c>
@@ -7657,13 +7658,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E154" s="2" t="n">
+      <c r="E154" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F154" s="2" t="n">
+      <c r="F154" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G154" s="3">
+      <c r="G154" s="5">
         <f>IF(AND(E154&lt;&gt;"",F154&lt;&gt;""),F154-E154,"")</f>
         <v/>
       </c>
@@ -7709,13 +7710,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E155" s="2" t="n">
+      <c r="E155" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F155" s="2" t="n">
+      <c r="F155" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G155" s="3">
+      <c r="G155" s="5">
         <f>IF(AND(E155&lt;&gt;"",F155&lt;&gt;""),F155-E155,"")</f>
         <v/>
       </c>
@@ -7761,13 +7762,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E156" s="2" t="n">
+      <c r="E156" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F156" s="2" t="n">
+      <c r="F156" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G156" s="3">
+      <c r="G156" s="5">
         <f>IF(AND(E156&lt;&gt;"",F156&lt;&gt;""),F156-E156,"")</f>
         <v/>
       </c>
@@ -7813,13 +7814,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E157" s="2" t="n">
+      <c r="E157" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F157" s="2" t="n">
+      <c r="F157" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G157" s="3">
+      <c r="G157" s="5">
         <f>IF(AND(E157&lt;&gt;"",F157&lt;&gt;""),F157-E157,"")</f>
         <v/>
       </c>
@@ -7865,13 +7866,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E158" s="2" t="n">
+      <c r="E158" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F158" s="2" t="n">
+      <c r="F158" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G158" s="3">
+      <c r="G158" s="5">
         <f>IF(AND(E158&lt;&gt;"",F158&lt;&gt;""),F158-E158,"")</f>
         <v/>
       </c>
@@ -7917,13 +7918,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E159" s="2" t="n">
+      <c r="E159" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F159" s="2" t="n">
+      <c r="F159" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G159" s="3">
+      <c r="G159" s="5">
         <f>IF(AND(E159&lt;&gt;"",F159&lt;&gt;""),F159-E159,"")</f>
         <v/>
       </c>
@@ -7969,13 +7970,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E160" s="2" t="n">
+      <c r="E160" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F160" s="2" t="n">
+      <c r="F160" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G160" s="3">
+      <c r="G160" s="5">
         <f>IF(AND(E160&lt;&gt;"",F160&lt;&gt;""),F160-E160,"")</f>
         <v/>
       </c>
@@ -8021,13 +8022,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E161" s="2" t="n">
+      <c r="E161" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F161" s="2" t="n">
+      <c r="F161" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G161" s="3">
+      <c r="G161" s="5">
         <f>IF(AND(E161&lt;&gt;"",F161&lt;&gt;""),F161-E161,"")</f>
         <v/>
       </c>
@@ -8073,13 +8074,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E162" s="2" t="n">
+      <c r="E162" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F162" s="2" t="n">
+      <c r="F162" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G162" s="3">
+      <c r="G162" s="5">
         <f>IF(AND(E162&lt;&gt;"",F162&lt;&gt;""),F162-E162,"")</f>
         <v/>
       </c>
@@ -8125,13 +8126,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E163" s="2" t="n">
+      <c r="E163" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F163" s="2" t="n">
+      <c r="F163" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G163" s="3">
+      <c r="G163" s="5">
         <f>IF(AND(E163&lt;&gt;"",F163&lt;&gt;""),F163-E163,"")</f>
         <v/>
       </c>
@@ -8177,13 +8178,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E164" s="2" t="n">
+      <c r="E164" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F164" s="2" t="n">
+      <c r="F164" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G164" s="3">
+      <c r="G164" s="5">
         <f>IF(AND(E164&lt;&gt;"",F164&lt;&gt;""),F164-E164,"")</f>
         <v/>
       </c>
@@ -8229,13 +8230,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E165" s="2" t="n">
+      <c r="E165" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F165" s="2" t="n">
+      <c r="F165" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G165" s="3">
+      <c r="G165" s="5">
         <f>IF(AND(E165&lt;&gt;"",F165&lt;&gt;""),F165-E165,"")</f>
         <v/>
       </c>
@@ -8281,13 +8282,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E166" s="2" t="n">
+      <c r="E166" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F166" s="2" t="n">
+      <c r="F166" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G166" s="3">
+      <c r="G166" s="5">
         <f>IF(AND(E166&lt;&gt;"",F166&lt;&gt;""),F166-E166,"")</f>
         <v/>
       </c>
@@ -8333,13 +8334,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E167" s="2" t="n">
+      <c r="E167" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F167" s="2" t="n">
+      <c r="F167" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G167" s="3">
+      <c r="G167" s="5">
         <f>IF(AND(E167&lt;&gt;"",F167&lt;&gt;""),F167-E167,"")</f>
         <v/>
       </c>
@@ -8385,13 +8386,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E168" s="2" t="n">
+      <c r="E168" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F168" s="2" t="n">
+      <c r="F168" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G168" s="3">
+      <c r="G168" s="5">
         <f>IF(AND(E168&lt;&gt;"",F168&lt;&gt;""),F168-E168,"")</f>
         <v/>
       </c>
@@ -8437,13 +8438,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E169" s="2" t="n">
+      <c r="E169" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F169" s="2" t="n">
+      <c r="F169" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G169" s="3">
+      <c r="G169" s="5">
         <f>IF(AND(E169&lt;&gt;"",F169&lt;&gt;""),F169-E169,"")</f>
         <v/>
       </c>
@@ -8489,13 +8490,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E170" s="2" t="n">
+      <c r="E170" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F170" s="2" t="n">
+      <c r="F170" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G170" s="3">
+      <c r="G170" s="5">
         <f>IF(AND(E170&lt;&gt;"",F170&lt;&gt;""),F170-E170,"")</f>
         <v/>
       </c>
@@ -8541,13 +8542,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E171" s="2" t="n">
+      <c r="E171" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F171" s="2" t="n">
+      <c r="F171" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G171" s="3">
+      <c r="G171" s="5">
         <f>IF(AND(E171&lt;&gt;"",F171&lt;&gt;""),F171-E171,"")</f>
         <v/>
       </c>
@@ -8593,13 +8594,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E172" s="2" t="n">
+      <c r="E172" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F172" s="2" t="n">
+      <c r="F172" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G172" s="3">
+      <c r="G172" s="5">
         <f>IF(AND(E172&lt;&gt;"",F172&lt;&gt;""),F172-E172,"")</f>
         <v/>
       </c>
@@ -8645,13 +8646,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E173" s="2" t="n">
+      <c r="E173" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F173" s="2" t="n">
+      <c r="F173" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G173" s="3">
+      <c r="G173" s="5">
         <f>IF(AND(E173&lt;&gt;"",F173&lt;&gt;""),F173-E173,"")</f>
         <v/>
       </c>
@@ -8697,13 +8698,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E174" s="2" t="n">
+      <c r="E174" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F174" s="2" t="n">
+      <c r="F174" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G174" s="3">
+      <c r="G174" s="5">
         <f>IF(AND(E174&lt;&gt;"",F174&lt;&gt;""),F174-E174,"")</f>
         <v/>
       </c>
@@ -8749,13 +8750,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E175" s="2" t="n">
+      <c r="E175" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F175" s="2" t="n">
+      <c r="F175" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G175" s="3">
+      <c r="G175" s="5">
         <f>IF(AND(E175&lt;&gt;"",F175&lt;&gt;""),F175-E175,"")</f>
         <v/>
       </c>
@@ -8801,13 +8802,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E176" s="2" t="n">
+      <c r="E176" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F176" s="2" t="n">
+      <c r="F176" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G176" s="3">
+      <c r="G176" s="5">
         <f>IF(AND(E176&lt;&gt;"",F176&lt;&gt;""),F176-E176,"")</f>
         <v/>
       </c>
@@ -8853,13 +8854,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E177" s="2" t="n">
+      <c r="E177" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F177" s="2" t="n">
+      <c r="F177" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G177" s="3">
+      <c r="G177" s="5">
         <f>IF(AND(E177&lt;&gt;"",F177&lt;&gt;""),F177-E177,"")</f>
         <v/>
       </c>
@@ -8905,13 +8906,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E178" s="2" t="n">
+      <c r="E178" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F178" s="2" t="n">
+      <c r="F178" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G178" s="3">
+      <c r="G178" s="5">
         <f>IF(AND(E178&lt;&gt;"",F178&lt;&gt;""),F178-E178,"")</f>
         <v/>
       </c>
@@ -8957,13 +8958,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E179" s="2" t="n">
+      <c r="E179" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F179" s="2" t="n">
+      <c r="F179" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G179" s="3">
+      <c r="G179" s="5">
         <f>IF(AND(E179&lt;&gt;"",F179&lt;&gt;""),F179-E179,"")</f>
         <v/>
       </c>
@@ -9009,13 +9010,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E180" s="2" t="n">
+      <c r="E180" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F180" s="2" t="n">
+      <c r="F180" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G180" s="3">
+      <c r="G180" s="5">
         <f>IF(AND(E180&lt;&gt;"",F180&lt;&gt;""),F180-E180,"")</f>
         <v/>
       </c>
@@ -9061,13 +9062,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E181" s="2" t="n">
+      <c r="E181" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F181" s="2" t="n">
+      <c r="F181" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G181" s="3">
+      <c r="G181" s="5">
         <f>IF(AND(E181&lt;&gt;"",F181&lt;&gt;""),F181-E181,"")</f>
         <v/>
       </c>
@@ -9113,13 +9114,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E182" s="2" t="n">
+      <c r="E182" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F182" s="2" t="n">
+      <c r="F182" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G182" s="3">
+      <c r="G182" s="5">
         <f>IF(AND(E182&lt;&gt;"",F182&lt;&gt;""),F182-E182,"")</f>
         <v/>
       </c>
@@ -9165,13 +9166,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E183" s="2" t="n">
+      <c r="E183" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F183" s="2" t="n">
+      <c r="F183" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G183" s="3">
+      <c r="G183" s="5">
         <f>IF(AND(E183&lt;&gt;"",F183&lt;&gt;""),F183-E183,"")</f>
         <v/>
       </c>
@@ -9217,13 +9218,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E184" s="2" t="n">
+      <c r="E184" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F184" s="2" t="n">
+      <c r="F184" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G184" s="3">
+      <c r="G184" s="5">
         <f>IF(AND(E184&lt;&gt;"",F184&lt;&gt;""),F184-E184,"")</f>
         <v/>
       </c>
@@ -9269,13 +9270,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E185" s="2" t="n">
+      <c r="E185" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F185" s="2" t="n">
+      <c r="F185" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G185" s="3">
+      <c r="G185" s="5">
         <f>IF(AND(E185&lt;&gt;"",F185&lt;&gt;""),F185-E185,"")</f>
         <v/>
       </c>
@@ -9321,13 +9322,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E186" s="2" t="n">
+      <c r="E186" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F186" s="2" t="n">
+      <c r="F186" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G186" s="3">
+      <c r="G186" s="5">
         <f>IF(AND(E186&lt;&gt;"",F186&lt;&gt;""),F186-E186,"")</f>
         <v/>
       </c>
@@ -9373,13 +9374,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E187" s="2" t="n">
+      <c r="E187" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F187" s="2" t="n">
+      <c r="F187" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G187" s="3">
+      <c r="G187" s="5">
         <f>IF(AND(E187&lt;&gt;"",F187&lt;&gt;""),F187-E187,"")</f>
         <v/>
       </c>
@@ -9425,13 +9426,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E188" s="2" t="n">
+      <c r="E188" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F188" s="2" t="n">
+      <c r="F188" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G188" s="3">
+      <c r="G188" s="5">
         <f>IF(AND(E188&lt;&gt;"",F188&lt;&gt;""),F188-E188,"")</f>
         <v/>
       </c>
@@ -9477,13 +9478,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E189" s="2" t="n">
+      <c r="E189" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F189" s="2" t="n">
+      <c r="F189" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G189" s="3">
+      <c r="G189" s="5">
         <f>IF(AND(E189&lt;&gt;"",F189&lt;&gt;""),F189-E189,"")</f>
         <v/>
       </c>
@@ -9529,13 +9530,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E190" s="2" t="n">
+      <c r="E190" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F190" s="2" t="n">
+      <c r="F190" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G190" s="3">
+      <c r="G190" s="5">
         <f>IF(AND(E190&lt;&gt;"",F190&lt;&gt;""),F190-E190,"")</f>
         <v/>
       </c>
@@ -9581,13 +9582,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E191" s="2" t="n">
+      <c r="E191" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F191" s="2" t="n">
+      <c r="F191" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G191" s="3">
+      <c r="G191" s="5">
         <f>IF(AND(E191&lt;&gt;"",F191&lt;&gt;""),F191-E191,"")</f>
         <v/>
       </c>
@@ -9633,13 +9634,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E192" s="2" t="n">
+      <c r="E192" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F192" s="2" t="n">
+      <c r="F192" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G192" s="3">
+      <c r="G192" s="5">
         <f>IF(AND(E192&lt;&gt;"",F192&lt;&gt;""),F192-E192,"")</f>
         <v/>
       </c>
@@ -9685,13 +9686,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E193" s="2" t="n">
+      <c r="E193" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F193" s="2" t="n">
+      <c r="F193" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G193" s="3">
+      <c r="G193" s="5">
         <f>IF(AND(E193&lt;&gt;"",F193&lt;&gt;""),F193-E193,"")</f>
         <v/>
       </c>
@@ -9737,13 +9738,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E194" s="2" t="n">
+      <c r="E194" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F194" s="2" t="n">
+      <c r="F194" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G194" s="3">
+      <c r="G194" s="5">
         <f>IF(AND(E194&lt;&gt;"",F194&lt;&gt;""),F194-E194,"")</f>
         <v/>
       </c>
@@ -9789,13 +9790,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E195" s="2" t="n">
+      <c r="E195" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F195" s="2" t="n">
+      <c r="F195" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G195" s="3">
+      <c r="G195" s="5">
         <f>IF(AND(E195&lt;&gt;"",F195&lt;&gt;""),F195-E195,"")</f>
         <v/>
       </c>
@@ -9841,13 +9842,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E196" s="2" t="n">
+      <c r="E196" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F196" s="2" t="n">
+      <c r="F196" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G196" s="3">
+      <c r="G196" s="5">
         <f>IF(AND(E196&lt;&gt;"",F196&lt;&gt;""),F196-E196,"")</f>
         <v/>
       </c>
@@ -9893,13 +9894,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E197" s="2" t="n">
+      <c r="E197" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F197" s="2" t="n">
+      <c r="F197" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G197" s="3">
+      <c r="G197" s="5">
         <f>IF(AND(E197&lt;&gt;"",F197&lt;&gt;""),F197-E197,"")</f>
         <v/>
       </c>
@@ -9945,13 +9946,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E198" s="2" t="n">
+      <c r="E198" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F198" s="2" t="n">
+      <c r="F198" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G198" s="3">
+      <c r="G198" s="5">
         <f>IF(AND(E198&lt;&gt;"",F198&lt;&gt;""),F198-E198,"")</f>
         <v/>
       </c>
@@ -9997,13 +9998,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E199" s="2" t="n">
+      <c r="E199" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F199" s="2" t="n">
+      <c r="F199" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G199" s="3">
+      <c r="G199" s="5">
         <f>IF(AND(E199&lt;&gt;"",F199&lt;&gt;""),F199-E199,"")</f>
         <v/>
       </c>
@@ -10049,13 +10050,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E200" s="2" t="n">
+      <c r="E200" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F200" s="2" t="n">
+      <c r="F200" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G200" s="3">
+      <c r="G200" s="5">
         <f>IF(AND(E200&lt;&gt;"",F200&lt;&gt;""),F200-E200,"")</f>
         <v/>
       </c>
@@ -10101,13 +10102,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E201" s="2" t="n">
+      <c r="E201" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F201" s="2" t="n">
+      <c r="F201" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G201" s="3">
+      <c r="G201" s="5">
         <f>IF(AND(E201&lt;&gt;"",F201&lt;&gt;""),F201-E201,"")</f>
         <v/>
       </c>
@@ -10153,13 +10154,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E202" s="2" t="n">
+      <c r="E202" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F202" s="2" t="n">
+      <c r="F202" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G202" s="3">
+      <c r="G202" s="5">
         <f>IF(AND(E202&lt;&gt;"",F202&lt;&gt;""),F202-E202,"")</f>
         <v/>
       </c>
@@ -10205,13 +10206,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E203" s="2" t="n">
+      <c r="E203" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F203" s="2" t="n">
+      <c r="F203" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G203" s="3">
+      <c r="G203" s="5">
         <f>IF(AND(E203&lt;&gt;"",F203&lt;&gt;""),F203-E203,"")</f>
         <v/>
       </c>
@@ -10257,13 +10258,13 @@
           <t>Service interruption of 129 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Jasin, Jasin 1, Ledang 1, Ledang, Muar 2, Batu Pahat 6, Yong Peng / Labis 1, Muar, Muar 1, Melaka Tengah 5, Batu Pahat 2, Batu Pahat 5, Yong Peng / Labis, Batu Pahat 3 area, Melaka, Johor</t>
         </is>
       </c>
-      <c r="E204" s="2" t="n">
+      <c r="E204" s="4" t="n">
         <v>46226.65694444445</v>
       </c>
-      <c r="F204" s="2" t="n">
+      <c r="F204" s="4" t="n">
         <v>46226.72152777778</v>
       </c>
-      <c r="G204" s="3">
+      <c r="G204" s="5">
         <f>IF(AND(E204&lt;&gt;"",F204&lt;&gt;""),F204-E204,"")</f>
         <v/>
       </c>
@@ -10309,13 +10310,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E205" s="2" t="n">
+      <c r="E205" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F205" s="2" t="n">
+      <c r="F205" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G205" s="3">
+      <c r="G205" s="5">
         <f>IF(AND(E205&lt;&gt;"",F205&lt;&gt;""),F205-E205,"")</f>
         <v/>
       </c>
@@ -10361,13 +10362,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E206" s="2" t="n">
+      <c r="E206" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F206" s="2" t="n">
+      <c r="F206" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G206" s="3">
+      <c r="G206" s="5">
         <f>IF(AND(E206&lt;&gt;"",F206&lt;&gt;""),F206-E206,"")</f>
         <v/>
       </c>
@@ -10413,13 +10414,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E207" s="2" t="n">
+      <c r="E207" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F207" s="2" t="n">
+      <c r="F207" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G207" s="3">
+      <c r="G207" s="5">
         <f>IF(AND(E207&lt;&gt;"",F207&lt;&gt;""),F207-E207,"")</f>
         <v/>
       </c>
@@ -10465,13 +10466,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E208" s="2" t="n">
+      <c r="E208" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F208" s="2" t="n">
+      <c r="F208" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G208" s="3">
+      <c r="G208" s="5">
         <f>IF(AND(E208&lt;&gt;"",F208&lt;&gt;""),F208-E208,"")</f>
         <v/>
       </c>
@@ -10517,13 +10518,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E209" s="2" t="n">
+      <c r="E209" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F209" s="2" t="n">
+      <c r="F209" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G209" s="3">
+      <c r="G209" s="5">
         <f>IF(AND(E209&lt;&gt;"",F209&lt;&gt;""),F209-E209,"")</f>
         <v/>
       </c>
@@ -10569,13 +10570,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E210" s="2" t="n">
+      <c r="E210" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F210" s="2" t="n">
+      <c r="F210" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G210" s="3">
+      <c r="G210" s="5">
         <f>IF(AND(E210&lt;&gt;"",F210&lt;&gt;""),F210-E210,"")</f>
         <v/>
       </c>
@@ -10621,13 +10622,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E211" s="2" t="n">
+      <c r="E211" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F211" s="2" t="n">
+      <c r="F211" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G211" s="3">
+      <c r="G211" s="5">
         <f>IF(AND(E211&lt;&gt;"",F211&lt;&gt;""),F211-E211,"")</f>
         <v/>
       </c>
@@ -10673,13 +10674,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E212" s="2" t="n">
+      <c r="E212" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F212" s="2" t="n">
+      <c r="F212" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G212" s="3">
+      <c r="G212" s="5">
         <f>IF(AND(E212&lt;&gt;"",F212&lt;&gt;""),F212-E212,"")</f>
         <v/>
       </c>
@@ -10725,13 +10726,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E213" s="2" t="n">
+      <c r="E213" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F213" s="2" t="n">
+      <c r="F213" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G213" s="3">
+      <c r="G213" s="5">
         <f>IF(AND(E213&lt;&gt;"",F213&lt;&gt;""),F213-E213,"")</f>
         <v/>
       </c>
@@ -10777,13 +10778,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E214" s="2" t="n">
+      <c r="E214" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F214" s="2" t="n">
+      <c r="F214" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G214" s="3">
+      <c r="G214" s="5">
         <f>IF(AND(E214&lt;&gt;"",F214&lt;&gt;""),F214-E214,"")</f>
         <v/>
       </c>
@@ -10829,13 +10830,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E215" s="2" t="n">
+      <c r="E215" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F215" s="2" t="n">
+      <c r="F215" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G215" s="3">
+      <c r="G215" s="5">
         <f>IF(AND(E215&lt;&gt;"",F215&lt;&gt;""),F215-E215,"")</f>
         <v/>
       </c>
@@ -10881,13 +10882,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E216" s="2" t="n">
+      <c r="E216" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F216" s="2" t="n">
+      <c r="F216" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G216" s="3">
+      <c r="G216" s="5">
         <f>IF(AND(E216&lt;&gt;"",F216&lt;&gt;""),F216-E216,"")</f>
         <v/>
       </c>
@@ -10933,13 +10934,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E217" s="2" t="n">
+      <c r="E217" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F217" s="2" t="n">
+      <c r="F217" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G217" s="3">
+      <c r="G217" s="5">
         <f>IF(AND(E217&lt;&gt;"",F217&lt;&gt;""),F217-E217,"")</f>
         <v/>
       </c>
@@ -10985,13 +10986,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E218" s="2" t="n">
+      <c r="E218" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F218" s="2" t="n">
+      <c r="F218" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G218" s="3">
+      <c r="G218" s="5">
         <f>IF(AND(E218&lt;&gt;"",F218&lt;&gt;""),F218-E218,"")</f>
         <v/>
       </c>
@@ -11037,13 +11038,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E219" s="2" t="n">
+      <c r="E219" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F219" s="2" t="n">
+      <c r="F219" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G219" s="3">
+      <c r="G219" s="5">
         <f>IF(AND(E219&lt;&gt;"",F219&lt;&gt;""),F219-E219,"")</f>
         <v/>
       </c>
@@ -11089,13 +11090,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E220" s="2" t="n">
+      <c r="E220" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F220" s="2" t="n">
+      <c r="F220" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G220" s="3">
+      <c r="G220" s="5">
         <f>IF(AND(E220&lt;&gt;"",F220&lt;&gt;""),F220-E220,"")</f>
         <v/>
       </c>
@@ -11141,13 +11142,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E221" s="2" t="n">
+      <c r="E221" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F221" s="2" t="n">
+      <c r="F221" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G221" s="3">
+      <c r="G221" s="5">
         <f>IF(AND(E221&lt;&gt;"",F221&lt;&gt;""),F221-E221,"")</f>
         <v/>
       </c>
@@ -11193,13 +11194,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E222" s="2" t="n">
+      <c r="E222" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F222" s="2" t="n">
+      <c r="F222" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G222" s="3">
+      <c r="G222" s="5">
         <f>IF(AND(E222&lt;&gt;"",F222&lt;&gt;""),F222-E222,"")</f>
         <v/>
       </c>
@@ -11245,13 +11246,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E223" s="2" t="n">
+      <c r="E223" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F223" s="2" t="n">
+      <c r="F223" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G223" s="3">
+      <c r="G223" s="5">
         <f>IF(AND(E223&lt;&gt;"",F223&lt;&gt;""),F223-E223,"")</f>
         <v/>
       </c>
@@ -11297,13 +11298,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E224" s="2" t="n">
+      <c r="E224" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F224" s="2" t="n">
+      <c r="F224" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G224" s="3">
+      <c r="G224" s="5">
         <f>IF(AND(E224&lt;&gt;"",F224&lt;&gt;""),F224-E224,"")</f>
         <v/>
       </c>
@@ -11349,13 +11350,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E225" s="2" t="n">
+      <c r="E225" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F225" s="2" t="n">
+      <c r="F225" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G225" s="3">
+      <c r="G225" s="5">
         <f>IF(AND(E225&lt;&gt;"",F225&lt;&gt;""),F225-E225,"")</f>
         <v/>
       </c>
@@ -11401,13 +11402,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E226" s="2" t="n">
+      <c r="E226" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F226" s="2" t="n">
+      <c r="F226" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G226" s="3">
+      <c r="G226" s="5">
         <f>IF(AND(E226&lt;&gt;"",F226&lt;&gt;""),F226-E226,"")</f>
         <v/>
       </c>
@@ -11453,13 +11454,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E227" s="2" t="n">
+      <c r="E227" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F227" s="2" t="n">
+      <c r="F227" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G227" s="3">
+      <c r="G227" s="5">
         <f>IF(AND(E227&lt;&gt;"",F227&lt;&gt;""),F227-E227,"")</f>
         <v/>
       </c>
@@ -11505,13 +11506,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E228" s="2" t="n">
+      <c r="E228" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F228" s="2" t="n">
+      <c r="F228" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G228" s="3">
+      <c r="G228" s="5">
         <f>IF(AND(E228&lt;&gt;"",F228&lt;&gt;""),F228-E228,"")</f>
         <v/>
       </c>
@@ -11557,13 +11558,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E229" s="2" t="n">
+      <c r="E229" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F229" s="2" t="n">
+      <c r="F229" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G229" s="3">
+      <c r="G229" s="5">
         <f>IF(AND(E229&lt;&gt;"",F229&lt;&gt;""),F229-E229,"")</f>
         <v/>
       </c>
@@ -11609,13 +11610,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E230" s="2" t="n">
+      <c r="E230" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F230" s="2" t="n">
+      <c r="F230" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G230" s="3">
+      <c r="G230" s="5">
         <f>IF(AND(E230&lt;&gt;"",F230&lt;&gt;""),F230-E230,"")</f>
         <v/>
       </c>
@@ -11661,13 +11662,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E231" s="2" t="n">
+      <c r="E231" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F231" s="2" t="n">
+      <c r="F231" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G231" s="3">
+      <c r="G231" s="5">
         <f>IF(AND(E231&lt;&gt;"",F231&lt;&gt;""),F231-E231,"")</f>
         <v/>
       </c>
@@ -11713,13 +11714,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E232" s="2" t="n">
+      <c r="E232" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F232" s="2" t="n">
+      <c r="F232" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G232" s="3">
+      <c r="G232" s="5">
         <f>IF(AND(E232&lt;&gt;"",F232&lt;&gt;""),F232-E232,"")</f>
         <v/>
       </c>
@@ -11765,13 +11766,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E233" s="2" t="n">
+      <c r="E233" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F233" s="2" t="n">
+      <c r="F233" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G233" s="3">
+      <c r="G233" s="5">
         <f>IF(AND(E233&lt;&gt;"",F233&lt;&gt;""),F233-E233,"")</f>
         <v/>
       </c>
@@ -11817,13 +11818,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E234" s="2" t="n">
+      <c r="E234" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F234" s="2" t="n">
+      <c r="F234" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G234" s="3">
+      <c r="G234" s="5">
         <f>IF(AND(E234&lt;&gt;"",F234&lt;&gt;""),F234-E234,"")</f>
         <v/>
       </c>
@@ -11869,13 +11870,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E235" s="2" t="n">
+      <c r="E235" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F235" s="2" t="n">
+      <c r="F235" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G235" s="3">
+      <c r="G235" s="5">
         <f>IF(AND(E235&lt;&gt;"",F235&lt;&gt;""),F235-E235,"")</f>
         <v/>
       </c>
@@ -11921,13 +11922,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E236" s="2" t="n">
+      <c r="E236" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F236" s="2" t="n">
+      <c r="F236" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G236" s="3">
+      <c r="G236" s="5">
         <f>IF(AND(E236&lt;&gt;"",F236&lt;&gt;""),F236-E236,"")</f>
         <v/>
       </c>
@@ -11973,13 +11974,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E237" s="2" t="n">
+      <c r="E237" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F237" s="2" t="n">
+      <c r="F237" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G237" s="3">
+      <c r="G237" s="5">
         <f>IF(AND(E237&lt;&gt;"",F237&lt;&gt;""),F237-E237,"")</f>
         <v/>
       </c>
@@ -12025,13 +12026,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E238" s="2" t="n">
+      <c r="E238" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F238" s="2" t="n">
+      <c r="F238" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G238" s="3">
+      <c r="G238" s="5">
         <f>IF(AND(E238&lt;&gt;"",F238&lt;&gt;""),F238-E238,"")</f>
         <v/>
       </c>
@@ -12077,13 +12078,13 @@
           <t>Service interruption of 25 (2G)(4G) xD and 10 (2G)(4G) xC sites at certain parts of Piasau, Limbang / Lawas, Permyjaya / Kuala Baram area, Sarawak</t>
         </is>
       </c>
-      <c r="E239" s="2" t="n">
+      <c r="E239" s="4" t="n">
         <v>46226.64236111111</v>
       </c>
-      <c r="F239" s="2" t="n">
+      <c r="F239" s="4" t="n">
         <v>46226.77708333333</v>
       </c>
-      <c r="G239" s="3">
+      <c r="G239" s="5">
         <f>IF(AND(E239&lt;&gt;"",F239&lt;&gt;""),F239-E239,"")</f>
         <v/>
       </c>
@@ -12129,13 +12130,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E240" s="2" t="n">
+      <c r="E240" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F240" s="2" t="n">
+      <c r="F240" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G240" s="3">
+      <c r="G240" s="5">
         <f>IF(AND(E240&lt;&gt;"",F240&lt;&gt;""),F240-E240,"")</f>
         <v/>
       </c>
@@ -12181,13 +12182,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E241" s="2" t="n">
+      <c r="E241" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F241" s="2" t="n">
+      <c r="F241" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G241" s="3">
+      <c r="G241" s="5">
         <f>IF(AND(E241&lt;&gt;"",F241&lt;&gt;""),F241-E241,"")</f>
         <v/>
       </c>
@@ -12233,13 +12234,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E242" s="2" t="n">
+      <c r="E242" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F242" s="2" t="n">
+      <c r="F242" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G242" s="3">
+      <c r="G242" s="5">
         <f>IF(AND(E242&lt;&gt;"",F242&lt;&gt;""),F242-E242,"")</f>
         <v/>
       </c>
@@ -12285,13 +12286,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E243" s="2" t="n">
+      <c r="E243" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F243" s="2" t="n">
+      <c r="F243" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G243" s="3">
+      <c r="G243" s="5">
         <f>IF(AND(E243&lt;&gt;"",F243&lt;&gt;""),F243-E243,"")</f>
         <v/>
       </c>
@@ -12337,13 +12338,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E244" s="2" t="n">
+      <c r="E244" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F244" s="2" t="n">
+      <c r="F244" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G244" s="3">
+      <c r="G244" s="5">
         <f>IF(AND(E244&lt;&gt;"",F244&lt;&gt;""),F244-E244,"")</f>
         <v/>
       </c>
@@ -12389,13 +12390,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E245" s="2" t="n">
+      <c r="E245" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F245" s="2" t="n">
+      <c r="F245" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G245" s="3">
+      <c r="G245" s="5">
         <f>IF(AND(E245&lt;&gt;"",F245&lt;&gt;""),F245-E245,"")</f>
         <v/>
       </c>
@@ -12441,13 +12442,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E246" s="2" t="n">
+      <c r="E246" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F246" s="2" t="n">
+      <c r="F246" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G246" s="3">
+      <c r="G246" s="5">
         <f>IF(AND(E246&lt;&gt;"",F246&lt;&gt;""),F246-E246,"")</f>
         <v/>
       </c>
@@ -12493,13 +12494,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E247" s="2" t="n">
+      <c r="E247" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F247" s="2" t="n">
+      <c r="F247" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G247" s="3">
+      <c r="G247" s="5">
         <f>IF(AND(E247&lt;&gt;"",F247&lt;&gt;""),F247-E247,"")</f>
         <v/>
       </c>
@@ -12545,13 +12546,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E248" s="2" t="n">
+      <c r="E248" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F248" s="2" t="n">
+      <c r="F248" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G248" s="3">
+      <c r="G248" s="5">
         <f>IF(AND(E248&lt;&gt;"",F248&lt;&gt;""),F248-E248,"")</f>
         <v/>
       </c>
@@ -12597,13 +12598,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E249" s="2" t="n">
+      <c r="E249" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F249" s="2" t="n">
+      <c r="F249" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G249" s="3">
+      <c r="G249" s="5">
         <f>IF(AND(E249&lt;&gt;"",F249&lt;&gt;""),F249-E249,"")</f>
         <v/>
       </c>
@@ -12649,13 +12650,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E250" s="2" t="n">
+      <c r="E250" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F250" s="2" t="n">
+      <c r="F250" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G250" s="3">
+      <c r="G250" s="5">
         <f>IF(AND(E250&lt;&gt;"",F250&lt;&gt;""),F250-E250,"")</f>
         <v/>
       </c>
@@ -12701,13 +12702,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E251" s="2" t="n">
+      <c r="E251" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F251" s="2" t="n">
+      <c r="F251" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G251" s="3">
+      <c r="G251" s="5">
         <f>IF(AND(E251&lt;&gt;"",F251&lt;&gt;""),F251-E251,"")</f>
         <v/>
       </c>
@@ -12753,13 +12754,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E252" s="2" t="n">
+      <c r="E252" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F252" s="2" t="n">
+      <c r="F252" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G252" s="3">
+      <c r="G252" s="5">
         <f>IF(AND(E252&lt;&gt;"",F252&lt;&gt;""),F252-E252,"")</f>
         <v/>
       </c>
@@ -12805,13 +12806,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E253" s="2" t="n">
+      <c r="E253" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F253" s="2" t="n">
+      <c r="F253" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G253" s="3">
+      <c r="G253" s="5">
         <f>IF(AND(E253&lt;&gt;"",F253&lt;&gt;""),F253-E253,"")</f>
         <v/>
       </c>
@@ -12857,13 +12858,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 6 (2G)(4G) xC sites at certain parts of Sarikei / Kanowit 2, Kapit, Sarikei / Kanowit 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E254" s="2" t="n">
+      <c r="E254" s="4" t="n">
         <v>46226.63125</v>
       </c>
-      <c r="F254" s="2" t="n">
+      <c r="F254" s="4" t="n">
         <v>46226.79027777778</v>
       </c>
-      <c r="G254" s="3">
+      <c r="G254" s="5">
         <f>IF(AND(E254&lt;&gt;"",F254&lt;&gt;""),F254-E254,"")</f>
         <v/>
       </c>
@@ -12909,10 +12910,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E255" s="2" t="n">
+      <c r="E255" s="4" t="n">
         <v>46226.58888888889</v>
       </c>
-      <c r="G255" s="3">
+      <c r="G255" s="5">
         <f>IF(AND(E255&lt;&gt;"",F255&lt;&gt;""),F255-E255,"")</f>
         <v/>
       </c>
@@ -12948,10 +12949,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E256" s="2" t="n">
+      <c r="E256" s="4" t="n">
         <v>46226.58888888889</v>
       </c>
-      <c r="G256" s="3">
+      <c r="G256" s="5">
         <f>IF(AND(E256&lt;&gt;"",F256&lt;&gt;""),F256-E256,"")</f>
         <v/>
       </c>
@@ -12987,10 +12988,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E257" s="2" t="n">
+      <c r="E257" s="4" t="n">
         <v>46226.58888888889</v>
       </c>
-      <c r="G257" s="3">
+      <c r="G257" s="5">
         <f>IF(AND(E257&lt;&gt;"",F257&lt;&gt;""),F257-E257,"")</f>
         <v/>
       </c>
@@ -13026,10 +13027,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E258" s="2" t="n">
+      <c r="E258" s="4" t="n">
         <v>46226.58888888889</v>
       </c>
-      <c r="G258" s="3">
+      <c r="G258" s="5">
         <f>IF(AND(E258&lt;&gt;"",F258&lt;&gt;""),F258-E258,"")</f>
         <v/>
       </c>
@@ -13060,10 +13061,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E259" s="2" t="n">
+      <c r="E259" s="4" t="n">
         <v>46226.58888888889</v>
       </c>
-      <c r="G259" s="3">
+      <c r="G259" s="5">
         <f>IF(AND(E259&lt;&gt;"",F259&lt;&gt;""),F259-E259,"")</f>
         <v/>
       </c>
@@ -13094,10 +13095,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E260" s="2" t="n">
+      <c r="E260" s="4" t="n">
         <v>46226.58888888889</v>
       </c>
-      <c r="G260" s="3">
+      <c r="G260" s="5">
         <f>IF(AND(E260&lt;&gt;"",F260&lt;&gt;""),F260-E260,"")</f>
         <v/>
       </c>
@@ -13133,13 +13134,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E261" s="2" t="n">
+      <c r="E261" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F261" s="2" t="n">
+      <c r="F261" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G261" s="3">
+      <c r="G261" s="5">
         <f>IF(AND(E261&lt;&gt;"",F261&lt;&gt;""),F261-E261,"")</f>
         <v/>
       </c>
@@ -13185,13 +13186,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E262" s="2" t="n">
+      <c r="E262" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F262" s="2" t="n">
+      <c r="F262" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G262" s="3">
+      <c r="G262" s="5">
         <f>IF(AND(E262&lt;&gt;"",F262&lt;&gt;""),F262-E262,"")</f>
         <v/>
       </c>
@@ -13237,13 +13238,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E263" s="2" t="n">
+      <c r="E263" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F263" s="2" t="n">
+      <c r="F263" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G263" s="3">
+      <c r="G263" s="5">
         <f>IF(AND(E263&lt;&gt;"",F263&lt;&gt;""),F263-E263,"")</f>
         <v/>
       </c>
@@ -13289,13 +13290,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E264" s="2" t="n">
+      <c r="E264" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F264" s="2" t="n">
+      <c r="F264" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G264" s="3">
+      <c r="G264" s="5">
         <f>IF(AND(E264&lt;&gt;"",F264&lt;&gt;""),F264-E264,"")</f>
         <v/>
       </c>
@@ -13341,13 +13342,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E265" s="2" t="n">
+      <c r="E265" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F265" s="2" t="n">
+      <c r="F265" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G265" s="3">
+      <c r="G265" s="5">
         <f>IF(AND(E265&lt;&gt;"",F265&lt;&gt;""),F265-E265,"")</f>
         <v/>
       </c>
@@ -13393,13 +13394,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E266" s="2" t="n">
+      <c r="E266" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F266" s="2" t="n">
+      <c r="F266" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G266" s="3">
+      <c r="G266" s="5">
         <f>IF(AND(E266&lt;&gt;"",F266&lt;&gt;""),F266-E266,"")</f>
         <v/>
       </c>
@@ -13445,13 +13446,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E267" s="2" t="n">
+      <c r="E267" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F267" s="2" t="n">
+      <c r="F267" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G267" s="3">
+      <c r="G267" s="5">
         <f>IF(AND(E267&lt;&gt;"",F267&lt;&gt;""),F267-E267,"")</f>
         <v/>
       </c>
@@ -13497,13 +13498,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E268" s="2" t="n">
+      <c r="E268" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F268" s="2" t="n">
+      <c r="F268" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G268" s="3">
+      <c r="G268" s="5">
         <f>IF(AND(E268&lt;&gt;"",F268&lt;&gt;""),F268-E268,"")</f>
         <v/>
       </c>
@@ -13549,13 +13550,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E269" s="2" t="n">
+      <c r="E269" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F269" s="2" t="n">
+      <c r="F269" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G269" s="3">
+      <c r="G269" s="5">
         <f>IF(AND(E269&lt;&gt;"",F269&lt;&gt;""),F269-E269,"")</f>
         <v/>
       </c>
@@ -13601,13 +13602,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E270" s="2" t="n">
+      <c r="E270" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F270" s="2" t="n">
+      <c r="F270" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G270" s="3">
+      <c r="G270" s="5">
         <f>IF(AND(E270&lt;&gt;"",F270&lt;&gt;""),F270-E270,"")</f>
         <v/>
       </c>
@@ -13653,13 +13654,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E271" s="2" t="n">
+      <c r="E271" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F271" s="2" t="n">
+      <c r="F271" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G271" s="3">
+      <c r="G271" s="5">
         <f>IF(AND(E271&lt;&gt;"",F271&lt;&gt;""),F271-E271,"")</f>
         <v/>
       </c>
@@ -13705,13 +13706,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E272" s="2" t="n">
+      <c r="E272" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F272" s="2" t="n">
+      <c r="F272" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G272" s="3">
+      <c r="G272" s="5">
         <f>IF(AND(E272&lt;&gt;"",F272&lt;&gt;""),F272-E272,"")</f>
         <v/>
       </c>
@@ -13757,13 +13758,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E273" s="2" t="n">
+      <c r="E273" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F273" s="2" t="n">
+      <c r="F273" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G273" s="3">
+      <c r="G273" s="5">
         <f>IF(AND(E273&lt;&gt;"",F273&lt;&gt;""),F273-E273,"")</f>
         <v/>
       </c>
@@ -13809,13 +13810,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E274" s="2" t="n">
+      <c r="E274" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F274" s="2" t="n">
+      <c r="F274" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G274" s="3">
+      <c r="G274" s="5">
         <f>IF(AND(E274&lt;&gt;"",F274&lt;&gt;""),F274-E274,"")</f>
         <v/>
       </c>
@@ -13861,13 +13862,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E275" s="2" t="n">
+      <c r="E275" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F275" s="2" t="n">
+      <c r="F275" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G275" s="3">
+      <c r="G275" s="5">
         <f>IF(AND(E275&lt;&gt;"",F275&lt;&gt;""),F275-E275,"")</f>
         <v/>
       </c>
@@ -13913,13 +13914,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E276" s="2" t="n">
+      <c r="E276" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F276" s="2" t="n">
+      <c r="F276" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G276" s="3">
+      <c r="G276" s="5">
         <f>IF(AND(E276&lt;&gt;"",F276&lt;&gt;""),F276-E276,"")</f>
         <v/>
       </c>
@@ -13965,13 +13966,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E277" s="2" t="n">
+      <c r="E277" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F277" s="2" t="n">
+      <c r="F277" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G277" s="3">
+      <c r="G277" s="5">
         <f>IF(AND(E277&lt;&gt;"",F277&lt;&gt;""),F277-E277,"")</f>
         <v/>
       </c>
@@ -14017,13 +14018,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E278" s="2" t="n">
+      <c r="E278" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F278" s="2" t="n">
+      <c r="F278" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G278" s="3">
+      <c r="G278" s="5">
         <f>IF(AND(E278&lt;&gt;"",F278&lt;&gt;""),F278-E278,"")</f>
         <v/>
       </c>
@@ -14069,13 +14070,13 @@
           <t>Service interruption of 12 (2G)(4G) xD and 7 (2G)(4G) xC sites at certain parts of Mukah / Matu Daro, Sarikei / Kanowit area, Sarawak</t>
         </is>
       </c>
-      <c r="E279" s="2" t="n">
+      <c r="E279" s="4" t="n">
         <v>46226.575</v>
       </c>
-      <c r="F279" s="2" t="n">
+      <c r="F279" s="4" t="n">
         <v>46227.00069444445</v>
       </c>
-      <c r="G279" s="3">
+      <c r="G279" s="5">
         <f>IF(AND(E279&lt;&gt;"",F279&lt;&gt;""),F279-E279,"")</f>
         <v/>
       </c>
@@ -14121,10 +14122,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Sri Aman / Betong 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E280" s="2" t="n">
+      <c r="E280" s="4" t="n">
         <v>46226.55208333334</v>
       </c>
-      <c r="G280" s="3">
+      <c r="G280" s="5">
         <f>IF(AND(E280&lt;&gt;"",F280&lt;&gt;""),F280-E280,"")</f>
         <v/>
       </c>
@@ -14160,10 +14161,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Sri Aman / Betong 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E281" s="2" t="n">
+      <c r="E281" s="4" t="n">
         <v>46226.55208333334</v>
       </c>
-      <c r="G281" s="3">
+      <c r="G281" s="5">
         <f>IF(AND(E281&lt;&gt;"",F281&lt;&gt;""),F281-E281,"")</f>
         <v/>
       </c>
@@ -14199,10 +14200,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Sri Aman / Betong 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E282" s="2" t="n">
+      <c r="E282" s="4" t="n">
         <v>46226.55208333334</v>
       </c>
-      <c r="G282" s="3">
+      <c r="G282" s="5">
         <f>IF(AND(E282&lt;&gt;"",F282&lt;&gt;""),F282-E282,"")</f>
         <v/>
       </c>
@@ -14238,10 +14239,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Sri Aman / Betong 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E283" s="2" t="n">
+      <c r="E283" s="4" t="n">
         <v>46226.55208333334</v>
       </c>
-      <c r="G283" s="3">
+      <c r="G283" s="5">
         <f>IF(AND(E283&lt;&gt;"",F283&lt;&gt;""),F283-E283,"")</f>
         <v/>
       </c>
@@ -14277,10 +14278,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Sri Aman / Betong 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E284" s="2" t="n">
+      <c r="E284" s="4" t="n">
         <v>46226.55208333334</v>
       </c>
-      <c r="G284" s="3">
+      <c r="G284" s="5">
         <f>IF(AND(E284&lt;&gt;"",F284&lt;&gt;""),F284-E284,"")</f>
         <v/>
       </c>
@@ -14316,10 +14317,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Sri Aman / Betong 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E285" s="2" t="n">
+      <c r="E285" s="4" t="n">
         <v>46226.55208333334</v>
       </c>
-      <c r="G285" s="3">
+      <c r="G285" s="5">
         <f>IF(AND(E285&lt;&gt;"",F285&lt;&gt;""),F285-E285,"")</f>
         <v/>
       </c>
@@ -14355,10 +14356,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Sri Aman / Betong 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E286" s="2" t="n">
+      <c r="E286" s="4" t="n">
         <v>46226.55208333334</v>
       </c>
-      <c r="G286" s="3">
+      <c r="G286" s="5">
         <f>IF(AND(E286&lt;&gt;"",F286&lt;&gt;""),F286-E286,"")</f>
         <v/>
       </c>
@@ -14394,10 +14395,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Sri Aman / Betong 1 area, Sarawak</t>
         </is>
       </c>
-      <c r="E287" s="2" t="n">
+      <c r="E287" s="4" t="n">
         <v>46226.55208333334</v>
       </c>
-      <c r="G287" s="3">
+      <c r="G287" s="5">
         <f>IF(AND(E287&lt;&gt;"",F287&lt;&gt;""),F287-E287,"")</f>
         <v/>
       </c>
@@ -14433,10 +14434,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Lipis area, Pahang</t>
         </is>
       </c>
-      <c r="E288" s="2" t="n">
+      <c r="E288" s="4" t="n">
         <v>46226.4625</v>
       </c>
-      <c r="G288" s="3">
+      <c r="G288" s="5">
         <f>IF(AND(E288&lt;&gt;"",F288&lt;&gt;""),F288-E288,"")</f>
         <v/>
       </c>
@@ -14472,10 +14473,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Lipis area, Pahang</t>
         </is>
       </c>
-      <c r="E289" s="2" t="n">
+      <c r="E289" s="4" t="n">
         <v>46226.4625</v>
       </c>
-      <c r="G289" s="3">
+      <c r="G289" s="5">
         <f>IF(AND(E289&lt;&gt;"",F289&lt;&gt;""),F289-E289,"")</f>
         <v/>
       </c>
@@ -14511,10 +14512,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Lipis area, Pahang</t>
         </is>
       </c>
-      <c r="E290" s="2" t="n">
+      <c r="E290" s="4" t="n">
         <v>46226.4625</v>
       </c>
-      <c r="G290" s="3">
+      <c r="G290" s="5">
         <f>IF(AND(E290&lt;&gt;"",F290&lt;&gt;""),F290-E290,"")</f>
         <v/>
       </c>
@@ -14550,10 +14551,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Lipis area, Pahang</t>
         </is>
       </c>
-      <c r="E291" s="2" t="n">
+      <c r="E291" s="4" t="n">
         <v>46226.4625</v>
       </c>
-      <c r="G291" s="3">
+      <c r="G291" s="5">
         <f>IF(AND(E291&lt;&gt;"",F291&lt;&gt;""),F291-E291,"")</f>
         <v/>
       </c>
@@ -14589,10 +14590,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Lipis area, Pahang</t>
         </is>
       </c>
-      <c r="E292" s="2" t="n">
+      <c r="E292" s="4" t="n">
         <v>46226.4625</v>
       </c>
-      <c r="G292" s="3">
+      <c r="G292" s="5">
         <f>IF(AND(E292&lt;&gt;"",F292&lt;&gt;""),F292-E292,"")</f>
         <v/>
       </c>
@@ -14628,10 +14629,10 @@
           <t>Service interruption of 1 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Lipis area, Pahang</t>
         </is>
       </c>
-      <c r="E293" s="2" t="n">
+      <c r="E293" s="4" t="n">
         <v>46226.4625</v>
       </c>
-      <c r="G293" s="3">
+      <c r="G293" s="5">
         <f>IF(AND(E293&lt;&gt;"",F293&lt;&gt;""),F293-E293,"")</f>
         <v/>
       </c>
@@ -14667,10 +14668,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Lunas, Kulim / Mahang area, Kedah</t>
         </is>
       </c>
-      <c r="E294" s="2" t="n">
+      <c r="E294" s="4" t="n">
         <v>46226.44930555556</v>
       </c>
-      <c r="G294" s="3">
+      <c r="G294" s="5">
         <f>IF(AND(E294&lt;&gt;"",F294&lt;&gt;""),F294-E294,"")</f>
         <v/>
       </c>
@@ -14706,10 +14707,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Lunas, Kulim / Mahang area, Kedah</t>
         </is>
       </c>
-      <c r="E295" s="2" t="n">
+      <c r="E295" s="4" t="n">
         <v>46226.44930555556</v>
       </c>
-      <c r="G295" s="3">
+      <c r="G295" s="5">
         <f>IF(AND(E295&lt;&gt;"",F295&lt;&gt;""),F295-E295,"")</f>
         <v/>
       </c>
@@ -14745,10 +14746,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Lunas, Kulim / Mahang area, Kedah</t>
         </is>
       </c>
-      <c r="E296" s="2" t="n">
+      <c r="E296" s="4" t="n">
         <v>46226.44930555556</v>
       </c>
-      <c r="G296" s="3">
+      <c r="G296" s="5">
         <f>IF(AND(E296&lt;&gt;"",F296&lt;&gt;""),F296-E296,"")</f>
         <v/>
       </c>
@@ -14784,10 +14785,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 1 (2G)(4G) xC sites at certain parts of Lunas, Kulim / Mahang area, Kedah</t>
         </is>
       </c>
-      <c r="E297" s="2" t="n">
+      <c r="E297" s="4" t="n">
         <v>46226.44930555556</v>
       </c>
-      <c r="G297" s="3">
+      <c r="G297" s="5">
         <f>IF(AND(E297&lt;&gt;"",F297&lt;&gt;""),F297-E297,"")</f>
         <v/>
       </c>
@@ -14823,10 +14824,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Bayan Lepas / Bpbd, Bayan Lepas / Bpbd 1 area, Penang</t>
         </is>
       </c>
-      <c r="E298" s="2" t="n">
+      <c r="E298" s="4" t="n">
         <v>46226.44583333333</v>
       </c>
-      <c r="G298" s="3">
+      <c r="G298" s="5">
         <f>IF(AND(E298&lt;&gt;"",F298&lt;&gt;""),F298-E298,"")</f>
         <v/>
       </c>
@@ -14862,10 +14863,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Bayan Lepas / Bpbd, Bayan Lepas / Bpbd 1 area, Penang</t>
         </is>
       </c>
-      <c r="E299" s="2" t="n">
+      <c r="E299" s="4" t="n">
         <v>46226.44583333333</v>
       </c>
-      <c r="G299" s="3">
+      <c r="G299" s="5">
         <f>IF(AND(E299&lt;&gt;"",F299&lt;&gt;""),F299-E299,"")</f>
         <v/>
       </c>
@@ -14901,10 +14902,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Bayan Lepas / Bpbd, Bayan Lepas / Bpbd 1 area, Penang</t>
         </is>
       </c>
-      <c r="E300" s="2" t="n">
+      <c r="E300" s="4" t="n">
         <v>46226.44583333333</v>
       </c>
-      <c r="G300" s="3">
+      <c r="G300" s="5">
         <f>IF(AND(E300&lt;&gt;"",F300&lt;&gt;""),F300-E300,"")</f>
         <v/>
       </c>
@@ -14940,10 +14941,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Bayan Lepas / Bpbd, Bayan Lepas / Bpbd 1 area, Penang</t>
         </is>
       </c>
-      <c r="E301" s="2" t="n">
+      <c r="E301" s="4" t="n">
         <v>46226.44583333333</v>
       </c>
-      <c r="G301" s="3">
+      <c r="G301" s="5">
         <f>IF(AND(E301&lt;&gt;"",F301&lt;&gt;""),F301-E301,"")</f>
         <v/>
       </c>
@@ -14979,10 +14980,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Bayan Lepas / Bpbd, Bayan Lepas / Bpbd 1 area, Penang</t>
         </is>
       </c>
-      <c r="E302" s="2" t="n">
+      <c r="E302" s="4" t="n">
         <v>46226.44583333333</v>
       </c>
-      <c r="G302" s="3">
+      <c r="G302" s="5">
         <f>IF(AND(E302&lt;&gt;"",F302&lt;&gt;""),F302-E302,"")</f>
         <v/>
       </c>
@@ -15018,10 +15019,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Bayan Lepas / Bpbd, Bayan Lepas / Bpbd 1 area, Penang</t>
         </is>
       </c>
-      <c r="E303" s="2" t="n">
+      <c r="E303" s="4" t="n">
         <v>46226.44583333333</v>
       </c>
-      <c r="G303" s="3">
+      <c r="G303" s="5">
         <f>IF(AND(E303&lt;&gt;"",F303&lt;&gt;""),F303-E303,"")</f>
         <v/>
       </c>
@@ -15057,10 +15058,10 @@
           <t>Service interruption of 7 (2G)(4G) xD sites at certain parts of Bayan Lepas / Bpbd, Bayan Lepas / Bpbd 1 area, Penang</t>
         </is>
       </c>
-      <c r="E304" s="2" t="n">
+      <c r="E304" s="4" t="n">
         <v>46226.44583333333</v>
       </c>
-      <c r="G304" s="3">
+      <c r="G304" s="5">
         <f>IF(AND(E304&lt;&gt;"",F304&lt;&gt;""),F304-E304,"")</f>
         <v/>
       </c>
@@ -15096,10 +15097,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E305" s="2" t="n">
+      <c r="E305" s="4" t="n">
         <v>46226.38194444445</v>
       </c>
-      <c r="G305" s="3">
+      <c r="G305" s="5">
         <f>IF(AND(E305&lt;&gt;"",F305&lt;&gt;""),F305-E305,"")</f>
         <v/>
       </c>
@@ -15135,10 +15136,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E306" s="2" t="n">
+      <c r="E306" s="4" t="n">
         <v>46226.38194444445</v>
       </c>
-      <c r="G306" s="3">
+      <c r="G306" s="5">
         <f>IF(AND(E306&lt;&gt;"",F306&lt;&gt;""),F306-E306,"")</f>
         <v/>
       </c>
@@ -15174,10 +15175,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E307" s="2" t="n">
+      <c r="E307" s="4" t="n">
         <v>46226.38194444445</v>
       </c>
-      <c r="G307" s="3">
+      <c r="G307" s="5">
         <f>IF(AND(E307&lt;&gt;"",F307&lt;&gt;""),F307-E307,"")</f>
         <v/>
       </c>
@@ -15213,10 +15214,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E308" s="2" t="n">
+      <c r="E308" s="4" t="n">
         <v>46226.38194444445</v>
       </c>
-      <c r="G308" s="3">
+      <c r="G308" s="5">
         <f>IF(AND(E308&lt;&gt;"",F308&lt;&gt;""),F308-E308,"")</f>
         <v/>
       </c>
@@ -15252,10 +15253,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E309" s="2" t="n">
+      <c r="E309" s="4" t="n">
         <v>46226.38194444445</v>
       </c>
-      <c r="G309" s="3">
+      <c r="G309" s="5">
         <f>IF(AND(E309&lt;&gt;"",F309&lt;&gt;""),F309-E309,"")</f>
         <v/>
       </c>
@@ -15286,10 +15287,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E310" s="2" t="n">
+      <c r="E310" s="4" t="n">
         <v>46226.38194444445</v>
       </c>
-      <c r="G310" s="3">
+      <c r="G310" s="5">
         <f>IF(AND(E310&lt;&gt;"",F310&lt;&gt;""),F310-E310,"")</f>
         <v/>
       </c>
@@ -15325,13 +15326,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E311" s="2" t="n">
+      <c r="E311" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F311" s="2" t="n">
+      <c r="F311" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G311" s="3">
+      <c r="G311" s="5">
         <f>IF(AND(E311&lt;&gt;"",F311&lt;&gt;""),F311-E311,"")</f>
         <v/>
       </c>
@@ -15377,13 +15378,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E312" s="2" t="n">
+      <c r="E312" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F312" s="2" t="n">
+      <c r="F312" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G312" s="3">
+      <c r="G312" s="5">
         <f>IF(AND(E312&lt;&gt;"",F312&lt;&gt;""),F312-E312,"")</f>
         <v/>
       </c>
@@ -15429,13 +15430,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E313" s="2" t="n">
+      <c r="E313" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F313" s="2" t="n">
+      <c r="F313" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G313" s="3">
+      <c r="G313" s="5">
         <f>IF(AND(E313&lt;&gt;"",F313&lt;&gt;""),F313-E313,"")</f>
         <v/>
       </c>
@@ -15481,13 +15482,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E314" s="2" t="n">
+      <c r="E314" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F314" s="2" t="n">
+      <c r="F314" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G314" s="3">
+      <c r="G314" s="5">
         <f>IF(AND(E314&lt;&gt;"",F314&lt;&gt;""),F314-E314,"")</f>
         <v/>
       </c>
@@ -15533,13 +15534,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E315" s="2" t="n">
+      <c r="E315" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F315" s="2" t="n">
+      <c r="F315" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G315" s="3">
+      <c r="G315" s="5">
         <f>IF(AND(E315&lt;&gt;"",F315&lt;&gt;""),F315-E315,"")</f>
         <v/>
       </c>
@@ -15585,13 +15586,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E316" s="2" t="n">
+      <c r="E316" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F316" s="2" t="n">
+      <c r="F316" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G316" s="3">
+      <c r="G316" s="5">
         <f>IF(AND(E316&lt;&gt;"",F316&lt;&gt;""),F316-E316,"")</f>
         <v/>
       </c>
@@ -15637,13 +15638,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E317" s="2" t="n">
+      <c r="E317" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F317" s="2" t="n">
+      <c r="F317" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G317" s="3">
+      <c r="G317" s="5">
         <f>IF(AND(E317&lt;&gt;"",F317&lt;&gt;""),F317-E317,"")</f>
         <v/>
       </c>
@@ -15689,13 +15690,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E318" s="2" t="n">
+      <c r="E318" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F318" s="2" t="n">
+      <c r="F318" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G318" s="3">
+      <c r="G318" s="5">
         <f>IF(AND(E318&lt;&gt;"",F318&lt;&gt;""),F318-E318,"")</f>
         <v/>
       </c>
@@ -15741,13 +15742,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E319" s="2" t="n">
+      <c r="E319" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F319" s="2" t="n">
+      <c r="F319" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G319" s="3">
+      <c r="G319" s="5">
         <f>IF(AND(E319&lt;&gt;"",F319&lt;&gt;""),F319-E319,"")</f>
         <v/>
       </c>
@@ -15793,13 +15794,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E320" s="2" t="n">
+      <c r="E320" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F320" s="2" t="n">
+      <c r="F320" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G320" s="3">
+      <c r="G320" s="5">
         <f>IF(AND(E320&lt;&gt;"",F320&lt;&gt;""),F320-E320,"")</f>
         <v/>
       </c>
@@ -15845,13 +15846,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E321" s="2" t="n">
+      <c r="E321" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F321" s="2" t="n">
+      <c r="F321" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G321" s="3">
+      <c r="G321" s="5">
         <f>IF(AND(E321&lt;&gt;"",F321&lt;&gt;""),F321-E321,"")</f>
         <v/>
       </c>
@@ -15897,13 +15898,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E322" s="2" t="n">
+      <c r="E322" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F322" s="2" t="n">
+      <c r="F322" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G322" s="3">
+      <c r="G322" s="5">
         <f>IF(AND(E322&lt;&gt;"",F322&lt;&gt;""),F322-E322,"")</f>
         <v/>
       </c>
@@ -15949,13 +15950,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E323" s="2" t="n">
+      <c r="E323" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F323" s="2" t="n">
+      <c r="F323" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G323" s="3">
+      <c r="G323" s="5">
         <f>IF(AND(E323&lt;&gt;"",F323&lt;&gt;""),F323-E323,"")</f>
         <v/>
       </c>
@@ -16001,13 +16002,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E324" s="2" t="n">
+      <c r="E324" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F324" s="2" t="n">
+      <c r="F324" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G324" s="3">
+      <c r="G324" s="5">
         <f>IF(AND(E324&lt;&gt;"",F324&lt;&gt;""),F324-E324,"")</f>
         <v/>
       </c>
@@ -16053,13 +16054,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E325" s="2" t="n">
+      <c r="E325" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F325" s="2" t="n">
+      <c r="F325" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G325" s="3">
+      <c r="G325" s="5">
         <f>IF(AND(E325&lt;&gt;"",F325&lt;&gt;""),F325-E325,"")</f>
         <v/>
       </c>
@@ -16105,13 +16106,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E326" s="2" t="n">
+      <c r="E326" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F326" s="2" t="n">
+      <c r="F326" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G326" s="3">
+      <c r="G326" s="5">
         <f>IF(AND(E326&lt;&gt;"",F326&lt;&gt;""),F326-E326,"")</f>
         <v/>
       </c>
@@ -16157,13 +16158,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E327" s="2" t="n">
+      <c r="E327" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F327" s="2" t="n">
+      <c r="F327" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G327" s="3">
+      <c r="G327" s="5">
         <f>IF(AND(E327&lt;&gt;"",F327&lt;&gt;""),F327-E327,"")</f>
         <v/>
       </c>
@@ -16209,13 +16210,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E328" s="2" t="n">
+      <c r="E328" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F328" s="2" t="n">
+      <c r="F328" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G328" s="3">
+      <c r="G328" s="5">
         <f>IF(AND(E328&lt;&gt;"",F328&lt;&gt;""),F328-E328,"")</f>
         <v/>
       </c>
@@ -16261,13 +16262,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E329" s="2" t="n">
+      <c r="E329" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F329" s="2" t="n">
+      <c r="F329" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G329" s="3">
+      <c r="G329" s="5">
         <f>IF(AND(E329&lt;&gt;"",F329&lt;&gt;""),F329-E329,"")</f>
         <v/>
       </c>
@@ -16313,13 +16314,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E330" s="2" t="n">
+      <c r="E330" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F330" s="2" t="n">
+      <c r="F330" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G330" s="3">
+      <c r="G330" s="5">
         <f>IF(AND(E330&lt;&gt;"",F330&lt;&gt;""),F330-E330,"")</f>
         <v/>
       </c>
@@ -16365,13 +16366,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E331" s="2" t="n">
+      <c r="E331" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F331" s="2" t="n">
+      <c r="F331" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G331" s="3">
+      <c r="G331" s="5">
         <f>IF(AND(E331&lt;&gt;"",F331&lt;&gt;""),F331-E331,"")</f>
         <v/>
       </c>
@@ -16417,13 +16418,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E332" s="2" t="n">
+      <c r="E332" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F332" s="2" t="n">
+      <c r="F332" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G332" s="3">
+      <c r="G332" s="5">
         <f>IF(AND(E332&lt;&gt;"",F332&lt;&gt;""),F332-E332,"")</f>
         <v/>
       </c>
@@ -16469,13 +16470,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E333" s="2" t="n">
+      <c r="E333" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F333" s="2" t="n">
+      <c r="F333" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G333" s="3">
+      <c r="G333" s="5">
         <f>IF(AND(E333&lt;&gt;"",F333&lt;&gt;""),F333-E333,"")</f>
         <v/>
       </c>
@@ -16521,13 +16522,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E334" s="2" t="n">
+      <c r="E334" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F334" s="2" t="n">
+      <c r="F334" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G334" s="3">
+      <c r="G334" s="5">
         <f>IF(AND(E334&lt;&gt;"",F334&lt;&gt;""),F334-E334,"")</f>
         <v/>
       </c>
@@ -16573,13 +16574,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E335" s="2" t="n">
+      <c r="E335" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F335" s="2" t="n">
+      <c r="F335" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G335" s="3">
+      <c r="G335" s="5">
         <f>IF(AND(E335&lt;&gt;"",F335&lt;&gt;""),F335-E335,"")</f>
         <v/>
       </c>
@@ -16625,13 +16626,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E336" s="2" t="n">
+      <c r="E336" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F336" s="2" t="n">
+      <c r="F336" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G336" s="3">
+      <c r="G336" s="5">
         <f>IF(AND(E336&lt;&gt;"",F336&lt;&gt;""),F336-E336,"")</f>
         <v/>
       </c>
@@ -16677,13 +16678,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E337" s="2" t="n">
+      <c r="E337" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F337" s="2" t="n">
+      <c r="F337" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G337" s="3">
+      <c r="G337" s="5">
         <f>IF(AND(E337&lt;&gt;"",F337&lt;&gt;""),F337-E337,"")</f>
         <v/>
       </c>
@@ -16729,13 +16730,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E338" s="2" t="n">
+      <c r="E338" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F338" s="2" t="n">
+      <c r="F338" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G338" s="3">
+      <c r="G338" s="5">
         <f>IF(AND(E338&lt;&gt;"",F338&lt;&gt;""),F338-E338,"")</f>
         <v/>
       </c>
@@ -16781,13 +16782,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E339" s="2" t="n">
+      <c r="E339" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F339" s="2" t="n">
+      <c r="F339" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G339" s="3">
+      <c r="G339" s="5">
         <f>IF(AND(E339&lt;&gt;"",F339&lt;&gt;""),F339-E339,"")</f>
         <v/>
       </c>
@@ -16833,13 +16834,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E340" s="2" t="n">
+      <c r="E340" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F340" s="2" t="n">
+      <c r="F340" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G340" s="3">
+      <c r="G340" s="5">
         <f>IF(AND(E340&lt;&gt;"",F340&lt;&gt;""),F340-E340,"")</f>
         <v/>
       </c>
@@ -16885,13 +16886,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E341" s="2" t="n">
+      <c r="E341" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F341" s="2" t="n">
+      <c r="F341" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G341" s="3">
+      <c r="G341" s="5">
         <f>IF(AND(E341&lt;&gt;"",F341&lt;&gt;""),F341-E341,"")</f>
         <v/>
       </c>
@@ -16937,13 +16938,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E342" s="2" t="n">
+      <c r="E342" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F342" s="2" t="n">
+      <c r="F342" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G342" s="3">
+      <c r="G342" s="5">
         <f>IF(AND(E342&lt;&gt;"",F342&lt;&gt;""),F342-E342,"")</f>
         <v/>
       </c>
@@ -16989,13 +16990,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E343" s="2" t="n">
+      <c r="E343" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F343" s="2" t="n">
+      <c r="F343" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G343" s="3">
+      <c r="G343" s="5">
         <f>IF(AND(E343&lt;&gt;"",F343&lt;&gt;""),F343-E343,"")</f>
         <v/>
       </c>
@@ -17041,13 +17042,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E344" s="2" t="n">
+      <c r="E344" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F344" s="2" t="n">
+      <c r="F344" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G344" s="3">
+      <c r="G344" s="5">
         <f>IF(AND(E344&lt;&gt;"",F344&lt;&gt;""),F344-E344,"")</f>
         <v/>
       </c>
@@ -17093,13 +17094,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E345" s="2" t="n">
+      <c r="E345" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F345" s="2" t="n">
+      <c r="F345" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G345" s="3">
+      <c r="G345" s="5">
         <f>IF(AND(E345&lt;&gt;"",F345&lt;&gt;""),F345-E345,"")</f>
         <v/>
       </c>
@@ -17145,13 +17146,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E346" s="2" t="n">
+      <c r="E346" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F346" s="2" t="n">
+      <c r="F346" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G346" s="3">
+      <c r="G346" s="5">
         <f>IF(AND(E346&lt;&gt;"",F346&lt;&gt;""),F346-E346,"")</f>
         <v/>
       </c>
@@ -17197,13 +17198,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E347" s="2" t="n">
+      <c r="E347" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F347" s="2" t="n">
+      <c r="F347" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G347" s="3">
+      <c r="G347" s="5">
         <f>IF(AND(E347&lt;&gt;"",F347&lt;&gt;""),F347-E347,"")</f>
         <v/>
       </c>
@@ -17249,13 +17250,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E348" s="2" t="n">
+      <c r="E348" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F348" s="2" t="n">
+      <c r="F348" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G348" s="3">
+      <c r="G348" s="5">
         <f>IF(AND(E348&lt;&gt;"",F348&lt;&gt;""),F348-E348,"")</f>
         <v/>
       </c>
@@ -17301,13 +17302,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E349" s="2" t="n">
+      <c r="E349" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F349" s="2" t="n">
+      <c r="F349" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G349" s="3">
+      <c r="G349" s="5">
         <f>IF(AND(E349&lt;&gt;"",F349&lt;&gt;""),F349-E349,"")</f>
         <v/>
       </c>
@@ -17353,13 +17354,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E350" s="2" t="n">
+      <c r="E350" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F350" s="2" t="n">
+      <c r="F350" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G350" s="3">
+      <c r="G350" s="5">
         <f>IF(AND(E350&lt;&gt;"",F350&lt;&gt;""),F350-E350,"")</f>
         <v/>
       </c>
@@ -17405,13 +17406,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E351" s="2" t="n">
+      <c r="E351" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F351" s="2" t="n">
+      <c r="F351" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G351" s="3">
+      <c r="G351" s="5">
         <f>IF(AND(E351&lt;&gt;"",F351&lt;&gt;""),F351-E351,"")</f>
         <v/>
       </c>
@@ -17457,13 +17458,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E352" s="2" t="n">
+      <c r="E352" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F352" s="2" t="n">
+      <c r="F352" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G352" s="3">
+      <c r="G352" s="5">
         <f>IF(AND(E352&lt;&gt;"",F352&lt;&gt;""),F352-E352,"")</f>
         <v/>
       </c>
@@ -17509,13 +17510,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E353" s="2" t="n">
+      <c r="E353" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F353" s="2" t="n">
+      <c r="F353" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G353" s="3">
+      <c r="G353" s="5">
         <f>IF(AND(E353&lt;&gt;"",F353&lt;&gt;""),F353-E353,"")</f>
         <v/>
       </c>
@@ -17561,13 +17562,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E354" s="2" t="n">
+      <c r="E354" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F354" s="2" t="n">
+      <c r="F354" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G354" s="3">
+      <c r="G354" s="5">
         <f>IF(AND(E354&lt;&gt;"",F354&lt;&gt;""),F354-E354,"")</f>
         <v/>
       </c>
@@ -17613,13 +17614,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E355" s="2" t="n">
+      <c r="E355" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F355" s="2" t="n">
+      <c r="F355" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G355" s="3">
+      <c r="G355" s="5">
         <f>IF(AND(E355&lt;&gt;"",F355&lt;&gt;""),F355-E355,"")</f>
         <v/>
       </c>
@@ -17665,13 +17666,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E356" s="2" t="n">
+      <c r="E356" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F356" s="2" t="n">
+      <c r="F356" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G356" s="3">
+      <c r="G356" s="5">
         <f>IF(AND(E356&lt;&gt;"",F356&lt;&gt;""),F356-E356,"")</f>
         <v/>
       </c>
@@ -17717,13 +17718,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E357" s="2" t="n">
+      <c r="E357" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F357" s="2" t="n">
+      <c r="F357" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G357" s="3">
+      <c r="G357" s="5">
         <f>IF(AND(E357&lt;&gt;"",F357&lt;&gt;""),F357-E357,"")</f>
         <v/>
       </c>
@@ -17769,13 +17770,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E358" s="2" t="n">
+      <c r="E358" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F358" s="2" t="n">
+      <c r="F358" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G358" s="3">
+      <c r="G358" s="5">
         <f>IF(AND(E358&lt;&gt;"",F358&lt;&gt;""),F358-E358,"")</f>
         <v/>
       </c>
@@ -17821,13 +17822,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E359" s="2" t="n">
+      <c r="E359" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F359" s="2" t="n">
+      <c r="F359" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G359" s="3">
+      <c r="G359" s="5">
         <f>IF(AND(E359&lt;&gt;"",F359&lt;&gt;""),F359-E359,"")</f>
         <v/>
       </c>
@@ -17873,13 +17874,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E360" s="2" t="n">
+      <c r="E360" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F360" s="2" t="n">
+      <c r="F360" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G360" s="3">
+      <c r="G360" s="5">
         <f>IF(AND(E360&lt;&gt;"",F360&lt;&gt;""),F360-E360,"")</f>
         <v/>
       </c>
@@ -17925,13 +17926,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E361" s="2" t="n">
+      <c r="E361" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F361" s="2" t="n">
+      <c r="F361" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G361" s="3">
+      <c r="G361" s="5">
         <f>IF(AND(E361&lt;&gt;"",F361&lt;&gt;""),F361-E361,"")</f>
         <v/>
       </c>
@@ -17977,13 +17978,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E362" s="2" t="n">
+      <c r="E362" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F362" s="2" t="n">
+      <c r="F362" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G362" s="3">
+      <c r="G362" s="5">
         <f>IF(AND(E362&lt;&gt;"",F362&lt;&gt;""),F362-E362,"")</f>
         <v/>
       </c>
@@ -18029,13 +18030,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E363" s="2" t="n">
+      <c r="E363" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F363" s="2" t="n">
+      <c r="F363" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G363" s="3">
+      <c r="G363" s="5">
         <f>IF(AND(E363&lt;&gt;"",F363&lt;&gt;""),F363-E363,"")</f>
         <v/>
       </c>
@@ -18081,13 +18082,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E364" s="2" t="n">
+      <c r="E364" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F364" s="2" t="n">
+      <c r="F364" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G364" s="3">
+      <c r="G364" s="5">
         <f>IF(AND(E364&lt;&gt;"",F364&lt;&gt;""),F364-E364,"")</f>
         <v/>
       </c>
@@ -18133,13 +18134,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E365" s="2" t="n">
+      <c r="E365" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F365" s="2" t="n">
+      <c r="F365" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G365" s="3">
+      <c r="G365" s="5">
         <f>IF(AND(E365&lt;&gt;"",F365&lt;&gt;""),F365-E365,"")</f>
         <v/>
       </c>
@@ -18185,13 +18186,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E366" s="2" t="n">
+      <c r="E366" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F366" s="2" t="n">
+      <c r="F366" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G366" s="3">
+      <c r="G366" s="5">
         <f>IF(AND(E366&lt;&gt;"",F366&lt;&gt;""),F366-E366,"")</f>
         <v/>
       </c>
@@ -18237,13 +18238,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E367" s="2" t="n">
+      <c r="E367" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F367" s="2" t="n">
+      <c r="F367" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G367" s="3">
+      <c r="G367" s="5">
         <f>IF(AND(E367&lt;&gt;"",F367&lt;&gt;""),F367-E367,"")</f>
         <v/>
       </c>
@@ -18289,13 +18290,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E368" s="2" t="n">
+      <c r="E368" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F368" s="2" t="n">
+      <c r="F368" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G368" s="3">
+      <c r="G368" s="5">
         <f>IF(AND(E368&lt;&gt;"",F368&lt;&gt;""),F368-E368,"")</f>
         <v/>
       </c>
@@ -18341,13 +18342,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E369" s="2" t="n">
+      <c r="E369" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F369" s="2" t="n">
+      <c r="F369" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G369" s="3">
+      <c r="G369" s="5">
         <f>IF(AND(E369&lt;&gt;"",F369&lt;&gt;""),F369-E369,"")</f>
         <v/>
       </c>
@@ -18393,13 +18394,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E370" s="2" t="n">
+      <c r="E370" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F370" s="2" t="n">
+      <c r="F370" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G370" s="3">
+      <c r="G370" s="5">
         <f>IF(AND(E370&lt;&gt;"",F370&lt;&gt;""),F370-E370,"")</f>
         <v/>
       </c>
@@ -18440,13 +18441,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E371" s="2" t="n">
+      <c r="E371" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F371" s="2" t="n">
+      <c r="F371" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G371" s="3">
+      <c r="G371" s="5">
         <f>IF(AND(E371&lt;&gt;"",F371&lt;&gt;""),F371-E371,"")</f>
         <v/>
       </c>
@@ -18487,13 +18488,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E372" s="2" t="n">
+      <c r="E372" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F372" s="2" t="n">
+      <c r="F372" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G372" s="3">
+      <c r="G372" s="5">
         <f>IF(AND(E372&lt;&gt;"",F372&lt;&gt;""),F372-E372,"")</f>
         <v/>
       </c>
@@ -18539,13 +18540,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E373" s="2" t="n">
+      <c r="E373" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F373" s="2" t="n">
+      <c r="F373" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G373" s="3">
+      <c r="G373" s="5">
         <f>IF(AND(E373&lt;&gt;"",F373&lt;&gt;""),F373-E373,"")</f>
         <v/>
       </c>
@@ -18591,13 +18592,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E374" s="2" t="n">
+      <c r="E374" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F374" s="2" t="n">
+      <c r="F374" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G374" s="3">
+      <c r="G374" s="5">
         <f>IF(AND(E374&lt;&gt;"",F374&lt;&gt;""),F374-E374,"")</f>
         <v/>
       </c>
@@ -18643,13 +18644,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E375" s="2" t="n">
+      <c r="E375" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F375" s="2" t="n">
+      <c r="F375" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G375" s="3">
+      <c r="G375" s="5">
         <f>IF(AND(E375&lt;&gt;"",F375&lt;&gt;""),F375-E375,"")</f>
         <v/>
       </c>
@@ -18695,13 +18696,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E376" s="2" t="n">
+      <c r="E376" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F376" s="2" t="n">
+      <c r="F376" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G376" s="3">
+      <c r="G376" s="5">
         <f>IF(AND(E376&lt;&gt;"",F376&lt;&gt;""),F376-E376,"")</f>
         <v/>
       </c>
@@ -18747,13 +18748,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E377" s="2" t="n">
+      <c r="E377" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F377" s="2" t="n">
+      <c r="F377" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G377" s="3">
+      <c r="G377" s="5">
         <f>IF(AND(E377&lt;&gt;"",F377&lt;&gt;""),F377-E377,"")</f>
         <v/>
       </c>
@@ -18799,13 +18800,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E378" s="2" t="n">
+      <c r="E378" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F378" s="2" t="n">
+      <c r="F378" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G378" s="3">
+      <c r="G378" s="5">
         <f>IF(AND(E378&lt;&gt;"",F378&lt;&gt;""),F378-E378,"")</f>
         <v/>
       </c>
@@ -18851,13 +18852,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E379" s="2" t="n">
+      <c r="E379" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F379" s="2" t="n">
+      <c r="F379" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G379" s="3">
+      <c r="G379" s="5">
         <f>IF(AND(E379&lt;&gt;"",F379&lt;&gt;""),F379-E379,"")</f>
         <v/>
       </c>
@@ -18903,13 +18904,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E380" s="2" t="n">
+      <c r="E380" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F380" s="2" t="n">
+      <c r="F380" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G380" s="3">
+      <c r="G380" s="5">
         <f>IF(AND(E380&lt;&gt;"",F380&lt;&gt;""),F380-E380,"")</f>
         <v/>
       </c>
@@ -18955,13 +18956,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E381" s="2" t="n">
+      <c r="E381" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F381" s="2" t="n">
+      <c r="F381" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G381" s="3">
+      <c r="G381" s="5">
         <f>IF(AND(E381&lt;&gt;"",F381&lt;&gt;""),F381-E381,"")</f>
         <v/>
       </c>
@@ -19007,13 +19008,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E382" s="2" t="n">
+      <c r="E382" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F382" s="2" t="n">
+      <c r="F382" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G382" s="3">
+      <c r="G382" s="5">
         <f>IF(AND(E382&lt;&gt;"",F382&lt;&gt;""),F382-E382,"")</f>
         <v/>
       </c>
@@ -19059,13 +19060,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E383" s="2" t="n">
+      <c r="E383" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F383" s="2" t="n">
+      <c r="F383" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G383" s="3">
+      <c r="G383" s="5">
         <f>IF(AND(E383&lt;&gt;"",F383&lt;&gt;""),F383-E383,"")</f>
         <v/>
       </c>
@@ -19111,13 +19112,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E384" s="2" t="n">
+      <c r="E384" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F384" s="2" t="n">
+      <c r="F384" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G384" s="3">
+      <c r="G384" s="5">
         <f>IF(AND(E384&lt;&gt;"",F384&lt;&gt;""),F384-E384,"")</f>
         <v/>
       </c>
@@ -19163,13 +19164,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E385" s="2" t="n">
+      <c r="E385" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F385" s="2" t="n">
+      <c r="F385" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G385" s="3">
+      <c r="G385" s="5">
         <f>IF(AND(E385&lt;&gt;"",F385&lt;&gt;""),F385-E385,"")</f>
         <v/>
       </c>
@@ -19215,13 +19216,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E386" s="2" t="n">
+      <c r="E386" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F386" s="2" t="n">
+      <c r="F386" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G386" s="3">
+      <c r="G386" s="5">
         <f>IF(AND(E386&lt;&gt;"",F386&lt;&gt;""),F386-E386,"")</f>
         <v/>
       </c>
@@ -19267,13 +19268,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E387" s="2" t="n">
+      <c r="E387" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F387" s="2" t="n">
+      <c r="F387" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G387" s="3">
+      <c r="G387" s="5">
         <f>IF(AND(E387&lt;&gt;"",F387&lt;&gt;""),F387-E387,"")</f>
         <v/>
       </c>
@@ -19319,13 +19320,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E388" s="2" t="n">
+      <c r="E388" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F388" s="2" t="n">
+      <c r="F388" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G388" s="3">
+      <c r="G388" s="5">
         <f>IF(AND(E388&lt;&gt;"",F388&lt;&gt;""),F388-E388,"")</f>
         <v/>
       </c>
@@ -19371,13 +19372,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E389" s="2" t="n">
+      <c r="E389" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F389" s="2" t="n">
+      <c r="F389" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G389" s="3">
+      <c r="G389" s="5">
         <f>IF(AND(E389&lt;&gt;"",F389&lt;&gt;""),F389-E389,"")</f>
         <v/>
       </c>
@@ -19423,13 +19424,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E390" s="2" t="n">
+      <c r="E390" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F390" s="2" t="n">
+      <c r="F390" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G390" s="3">
+      <c r="G390" s="5">
         <f>IF(AND(E390&lt;&gt;"",F390&lt;&gt;""),F390-E390,"")</f>
         <v/>
       </c>
@@ -19475,13 +19476,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E391" s="2" t="n">
+      <c r="E391" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F391" s="2" t="n">
+      <c r="F391" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G391" s="3">
+      <c r="G391" s="5">
         <f>IF(AND(E391&lt;&gt;"",F391&lt;&gt;""),F391-E391,"")</f>
         <v/>
       </c>
@@ -19527,13 +19528,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E392" s="2" t="n">
+      <c r="E392" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F392" s="2" t="n">
+      <c r="F392" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G392" s="3">
+      <c r="G392" s="5">
         <f>IF(AND(E392&lt;&gt;"",F392&lt;&gt;""),F392-E392,"")</f>
         <v/>
       </c>
@@ -19579,13 +19580,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E393" s="2" t="n">
+      <c r="E393" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F393" s="2" t="n">
+      <c r="F393" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G393" s="3">
+      <c r="G393" s="5">
         <f>IF(AND(E393&lt;&gt;"",F393&lt;&gt;""),F393-E393,"")</f>
         <v/>
       </c>
@@ -19631,13 +19632,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E394" s="2" t="n">
+      <c r="E394" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F394" s="2" t="n">
+      <c r="F394" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G394" s="3">
+      <c r="G394" s="5">
         <f>IF(AND(E394&lt;&gt;"",F394&lt;&gt;""),F394-E394,"")</f>
         <v/>
       </c>
@@ -19683,13 +19684,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E395" s="2" t="n">
+      <c r="E395" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F395" s="2" t="n">
+      <c r="F395" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G395" s="3">
+      <c r="G395" s="5">
         <f>IF(AND(E395&lt;&gt;"",F395&lt;&gt;""),F395-E395,"")</f>
         <v/>
       </c>
@@ -19735,13 +19736,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E396" s="2" t="n">
+      <c r="E396" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F396" s="2" t="n">
+      <c r="F396" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G396" s="3">
+      <c r="G396" s="5">
         <f>IF(AND(E396&lt;&gt;"",F396&lt;&gt;""),F396-E396,"")</f>
         <v/>
       </c>
@@ -19787,13 +19788,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E397" s="2" t="n">
+      <c r="E397" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F397" s="2" t="n">
+      <c r="F397" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G397" s="3">
+      <c r="G397" s="5">
         <f>IF(AND(E397&lt;&gt;"",F397&lt;&gt;""),F397-E397,"")</f>
         <v/>
       </c>
@@ -19839,13 +19840,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E398" s="2" t="n">
+      <c r="E398" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F398" s="2" t="n">
+      <c r="F398" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G398" s="3">
+      <c r="G398" s="5">
         <f>IF(AND(E398&lt;&gt;"",F398&lt;&gt;""),F398-E398,"")</f>
         <v/>
       </c>
@@ -19891,13 +19892,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E399" s="2" t="n">
+      <c r="E399" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F399" s="2" t="n">
+      <c r="F399" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G399" s="3">
+      <c r="G399" s="5">
         <f>IF(AND(E399&lt;&gt;"",F399&lt;&gt;""),F399-E399,"")</f>
         <v/>
       </c>
@@ -19943,13 +19944,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E400" s="2" t="n">
+      <c r="E400" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F400" s="2" t="n">
+      <c r="F400" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G400" s="3">
+      <c r="G400" s="5">
         <f>IF(AND(E400&lt;&gt;"",F400&lt;&gt;""),F400-E400,"")</f>
         <v/>
       </c>
@@ -19995,13 +19996,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E401" s="2" t="n">
+      <c r="E401" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F401" s="2" t="n">
+      <c r="F401" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G401" s="3">
+      <c r="G401" s="5">
         <f>IF(AND(E401&lt;&gt;"",F401&lt;&gt;""),F401-E401,"")</f>
         <v/>
       </c>
@@ -20047,13 +20048,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E402" s="2" t="n">
+      <c r="E402" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F402" s="2" t="n">
+      <c r="F402" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G402" s="3">
+      <c r="G402" s="5">
         <f>IF(AND(E402&lt;&gt;"",F402&lt;&gt;""),F402-E402,"")</f>
         <v/>
       </c>
@@ -20099,13 +20100,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E403" s="2" t="n">
+      <c r="E403" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F403" s="2" t="n">
+      <c r="F403" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G403" s="3">
+      <c r="G403" s="5">
         <f>IF(AND(E403&lt;&gt;"",F403&lt;&gt;""),F403-E403,"")</f>
         <v/>
       </c>
@@ -20151,13 +20152,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E404" s="2" t="n">
+      <c r="E404" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F404" s="2" t="n">
+      <c r="F404" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G404" s="3">
+      <c r="G404" s="5">
         <f>IF(AND(E404&lt;&gt;"",F404&lt;&gt;""),F404-E404,"")</f>
         <v/>
       </c>
@@ -20203,13 +20204,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E405" s="2" t="n">
+      <c r="E405" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F405" s="2" t="n">
+      <c r="F405" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G405" s="3">
+      <c r="G405" s="5">
         <f>IF(AND(E405&lt;&gt;"",F405&lt;&gt;""),F405-E405,"")</f>
         <v/>
       </c>
@@ -20255,13 +20256,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E406" s="2" t="n">
+      <c r="E406" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F406" s="2" t="n">
+      <c r="F406" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G406" s="3">
+      <c r="G406" s="5">
         <f>IF(AND(E406&lt;&gt;"",F406&lt;&gt;""),F406-E406,"")</f>
         <v/>
       </c>
@@ -20307,13 +20308,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E407" s="2" t="n">
+      <c r="E407" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F407" s="2" t="n">
+      <c r="F407" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G407" s="3">
+      <c r="G407" s="5">
         <f>IF(AND(E407&lt;&gt;"",F407&lt;&gt;""),F407-E407,"")</f>
         <v/>
       </c>
@@ -20359,13 +20360,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E408" s="2" t="n">
+      <c r="E408" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F408" s="2" t="n">
+      <c r="F408" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G408" s="3">
+      <c r="G408" s="5">
         <f>IF(AND(E408&lt;&gt;"",F408&lt;&gt;""),F408-E408,"")</f>
         <v/>
       </c>
@@ -20411,13 +20412,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E409" s="2" t="n">
+      <c r="E409" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F409" s="2" t="n">
+      <c r="F409" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G409" s="3">
+      <c r="G409" s="5">
         <f>IF(AND(E409&lt;&gt;"",F409&lt;&gt;""),F409-E409,"")</f>
         <v/>
       </c>
@@ -20463,13 +20464,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E410" s="2" t="n">
+      <c r="E410" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F410" s="2" t="n">
+      <c r="F410" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G410" s="3">
+      <c r="G410" s="5">
         <f>IF(AND(E410&lt;&gt;"",F410&lt;&gt;""),F410-E410,"")</f>
         <v/>
       </c>
@@ -20515,13 +20516,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E411" s="2" t="n">
+      <c r="E411" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F411" s="2" t="n">
+      <c r="F411" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G411" s="3">
+      <c r="G411" s="5">
         <f>IF(AND(E411&lt;&gt;"",F411&lt;&gt;""),F411-E411,"")</f>
         <v/>
       </c>
@@ -20567,13 +20568,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E412" s="2" t="n">
+      <c r="E412" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F412" s="2" t="n">
+      <c r="F412" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G412" s="3">
+      <c r="G412" s="5">
         <f>IF(AND(E412&lt;&gt;"",F412&lt;&gt;""),F412-E412,"")</f>
         <v/>
       </c>
@@ -20619,13 +20620,13 @@
           <t>Service interruption of 87 (2G)(4G) xD and 16 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Keningau, Tambunan, Tenom, Kota Marudu, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E413" s="2" t="n">
+      <c r="E413" s="4" t="n">
         <v>46226.38125</v>
       </c>
-      <c r="F413" s="2" t="n">
+      <c r="F413" s="4" t="n">
         <v>46226.39166666667</v>
       </c>
-      <c r="G413" s="3">
+      <c r="G413" s="5">
         <f>IF(AND(E413&lt;&gt;"",F413&lt;&gt;""),F413-E413,"")</f>
         <v/>
       </c>
@@ -20671,13 +20672,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E414" s="2" t="n">
+      <c r="E414" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F414" s="2" t="n">
+      <c r="F414" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G414" s="3">
+      <c r="G414" s="5">
         <f>IF(AND(E414&lt;&gt;"",F414&lt;&gt;""),F414-E414,"")</f>
         <v/>
       </c>
@@ -20723,13 +20724,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E415" s="2" t="n">
+      <c r="E415" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F415" s="2" t="n">
+      <c r="F415" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G415" s="3">
+      <c r="G415" s="5">
         <f>IF(AND(E415&lt;&gt;"",F415&lt;&gt;""),F415-E415,"")</f>
         <v/>
       </c>
@@ -20775,13 +20776,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E416" s="2" t="n">
+      <c r="E416" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F416" s="2" t="n">
+      <c r="F416" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G416" s="3">
+      <c r="G416" s="5">
         <f>IF(AND(E416&lt;&gt;"",F416&lt;&gt;""),F416-E416,"")</f>
         <v/>
       </c>
@@ -20827,13 +20828,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E417" s="2" t="n">
+      <c r="E417" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F417" s="2" t="n">
+      <c r="F417" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G417" s="3">
+      <c r="G417" s="5">
         <f>IF(AND(E417&lt;&gt;"",F417&lt;&gt;""),F417-E417,"")</f>
         <v/>
       </c>
@@ -20879,13 +20880,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E418" s="2" t="n">
+      <c r="E418" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F418" s="2" t="n">
+      <c r="F418" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G418" s="3">
+      <c r="G418" s="5">
         <f>IF(AND(E418&lt;&gt;"",F418&lt;&gt;""),F418-E418,"")</f>
         <v/>
       </c>
@@ -20931,13 +20932,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E419" s="2" t="n">
+      <c r="E419" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F419" s="2" t="n">
+      <c r="F419" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G419" s="3">
+      <c r="G419" s="5">
         <f>IF(AND(E419&lt;&gt;"",F419&lt;&gt;""),F419-E419,"")</f>
         <v/>
       </c>
@@ -20983,13 +20984,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E420" s="2" t="n">
+      <c r="E420" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F420" s="2" t="n">
+      <c r="F420" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G420" s="3">
+      <c r="G420" s="5">
         <f>IF(AND(E420&lt;&gt;"",F420&lt;&gt;""),F420-E420,"")</f>
         <v/>
       </c>
@@ -21035,13 +21036,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E421" s="2" t="n">
+      <c r="E421" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F421" s="2" t="n">
+      <c r="F421" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G421" s="3">
+      <c r="G421" s="5">
         <f>IF(AND(E421&lt;&gt;"",F421&lt;&gt;""),F421-E421,"")</f>
         <v/>
       </c>
@@ -21087,13 +21088,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E422" s="2" t="n">
+      <c r="E422" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F422" s="2" t="n">
+      <c r="F422" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G422" s="3">
+      <c r="G422" s="5">
         <f>IF(AND(E422&lt;&gt;"",F422&lt;&gt;""),F422-E422,"")</f>
         <v/>
       </c>
@@ -21139,13 +21140,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E423" s="2" t="n">
+      <c r="E423" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F423" s="2" t="n">
+      <c r="F423" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G423" s="3">
+      <c r="G423" s="5">
         <f>IF(AND(E423&lt;&gt;"",F423&lt;&gt;""),F423-E423,"")</f>
         <v/>
       </c>
@@ -21191,13 +21192,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E424" s="2" t="n">
+      <c r="E424" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F424" s="2" t="n">
+      <c r="F424" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G424" s="3">
+      <c r="G424" s="5">
         <f>IF(AND(E424&lt;&gt;"",F424&lt;&gt;""),F424-E424,"")</f>
         <v/>
       </c>
@@ -21243,13 +21244,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E425" s="2" t="n">
+      <c r="E425" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F425" s="2" t="n">
+      <c r="F425" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G425" s="3">
+      <c r="G425" s="5">
         <f>IF(AND(E425&lt;&gt;"",F425&lt;&gt;""),F425-E425,"")</f>
         <v/>
       </c>
@@ -21295,13 +21296,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E426" s="2" t="n">
+      <c r="E426" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F426" s="2" t="n">
+      <c r="F426" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G426" s="3">
+      <c r="G426" s="5">
         <f>IF(AND(E426&lt;&gt;"",F426&lt;&gt;""),F426-E426,"")</f>
         <v/>
       </c>
@@ -21347,13 +21348,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E427" s="2" t="n">
+      <c r="E427" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F427" s="2" t="n">
+      <c r="F427" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G427" s="3">
+      <c r="G427" s="5">
         <f>IF(AND(E427&lt;&gt;"",F427&lt;&gt;""),F427-E427,"")</f>
         <v/>
       </c>
@@ -21399,13 +21400,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E428" s="2" t="n">
+      <c r="E428" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F428" s="2" t="n">
+      <c r="F428" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G428" s="3">
+      <c r="G428" s="5">
         <f>IF(AND(E428&lt;&gt;"",F428&lt;&gt;""),F428-E428,"")</f>
         <v/>
       </c>
@@ -21451,13 +21452,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E429" s="2" t="n">
+      <c r="E429" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F429" s="2" t="n">
+      <c r="F429" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G429" s="3">
+      <c r="G429" s="5">
         <f>IF(AND(E429&lt;&gt;"",F429&lt;&gt;""),F429-E429,"")</f>
         <v/>
       </c>
@@ -21503,13 +21504,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E430" s="2" t="n">
+      <c r="E430" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F430" s="2" t="n">
+      <c r="F430" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G430" s="3">
+      <c r="G430" s="5">
         <f>IF(AND(E430&lt;&gt;"",F430&lt;&gt;""),F430-E430,"")</f>
         <v/>
       </c>
@@ -21555,13 +21556,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E431" s="2" t="n">
+      <c r="E431" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F431" s="2" t="n">
+      <c r="F431" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G431" s="3">
+      <c r="G431" s="5">
         <f>IF(AND(E431&lt;&gt;"",F431&lt;&gt;""),F431-E431,"")</f>
         <v/>
       </c>
@@ -21607,13 +21608,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E432" s="2" t="n">
+      <c r="E432" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F432" s="2" t="n">
+      <c r="F432" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G432" s="3">
+      <c r="G432" s="5">
         <f>IF(AND(E432&lt;&gt;"",F432&lt;&gt;""),F432-E432,"")</f>
         <v/>
       </c>
@@ -21659,13 +21660,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E433" s="2" t="n">
+      <c r="E433" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F433" s="2" t="n">
+      <c r="F433" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G433" s="3">
+      <c r="G433" s="5">
         <f>IF(AND(E433&lt;&gt;"",F433&lt;&gt;""),F433-E433,"")</f>
         <v/>
       </c>
@@ -21711,13 +21712,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E434" s="2" t="n">
+      <c r="E434" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F434" s="2" t="n">
+      <c r="F434" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G434" s="3">
+      <c r="G434" s="5">
         <f>IF(AND(E434&lt;&gt;"",F434&lt;&gt;""),F434-E434,"")</f>
         <v/>
       </c>
@@ -21763,13 +21764,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E435" s="2" t="n">
+      <c r="E435" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F435" s="2" t="n">
+      <c r="F435" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G435" s="3">
+      <c r="G435" s="5">
         <f>IF(AND(E435&lt;&gt;"",F435&lt;&gt;""),F435-E435,"")</f>
         <v/>
       </c>
@@ -21815,13 +21816,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E436" s="2" t="n">
+      <c r="E436" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F436" s="2" t="n">
+      <c r="F436" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G436" s="3">
+      <c r="G436" s="5">
         <f>IF(AND(E436&lt;&gt;"",F436&lt;&gt;""),F436-E436,"")</f>
         <v/>
       </c>
@@ -21867,13 +21868,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E437" s="2" t="n">
+      <c r="E437" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F437" s="2" t="n">
+      <c r="F437" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G437" s="3">
+      <c r="G437" s="5">
         <f>IF(AND(E437&lt;&gt;"",F437&lt;&gt;""),F437-E437,"")</f>
         <v/>
       </c>
@@ -21919,13 +21920,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E438" s="2" t="n">
+      <c r="E438" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F438" s="2" t="n">
+      <c r="F438" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G438" s="3">
+      <c r="G438" s="5">
         <f>IF(AND(E438&lt;&gt;"",F438&lt;&gt;""),F438-E438,"")</f>
         <v/>
       </c>
@@ -21971,13 +21972,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E439" s="2" t="n">
+      <c r="E439" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F439" s="2" t="n">
+      <c r="F439" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G439" s="3">
+      <c r="G439" s="5">
         <f>IF(AND(E439&lt;&gt;"",F439&lt;&gt;""),F439-E439,"")</f>
         <v/>
       </c>
@@ -22023,13 +22024,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E440" s="2" t="n">
+      <c r="E440" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F440" s="2" t="n">
+      <c r="F440" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G440" s="3">
+      <c r="G440" s="5">
         <f>IF(AND(E440&lt;&gt;"",F440&lt;&gt;""),F440-E440,"")</f>
         <v/>
       </c>
@@ -22075,13 +22076,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E441" s="2" t="n">
+      <c r="E441" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F441" s="2" t="n">
+      <c r="F441" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G441" s="3">
+      <c r="G441" s="5">
         <f>IF(AND(E441&lt;&gt;"",F441&lt;&gt;""),F441-E441,"")</f>
         <v/>
       </c>
@@ -22127,13 +22128,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E442" s="2" t="n">
+      <c r="E442" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F442" s="2" t="n">
+      <c r="F442" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G442" s="3">
+      <c r="G442" s="5">
         <f>IF(AND(E442&lt;&gt;"",F442&lt;&gt;""),F442-E442,"")</f>
         <v/>
       </c>
@@ -22179,13 +22180,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E443" s="2" t="n">
+      <c r="E443" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F443" s="2" t="n">
+      <c r="F443" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G443" s="3">
+      <c r="G443" s="5">
         <f>IF(AND(E443&lt;&gt;"",F443&lt;&gt;""),F443-E443,"")</f>
         <v/>
       </c>
@@ -22231,13 +22232,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E444" s="2" t="n">
+      <c r="E444" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="F444" s="2" t="n">
+      <c r="F444" s="4" t="n">
         <v>46226.35486111111</v>
       </c>
-      <c r="G444" s="3">
+      <c r="G444" s="5">
         <f>IF(AND(E444&lt;&gt;"",F444&lt;&gt;""),F444-E444,"")</f>
         <v/>
       </c>
@@ -22278,10 +22279,10 @@
           <t>Service interruption of 28 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Keningau 1, Ranau, Tenom, Sipitang 1 area, Sabah</t>
         </is>
       </c>
-      <c r="E445" s="2" t="n">
+      <c r="E445" s="4" t="n">
         <v>46226.34375</v>
       </c>
-      <c r="G445" s="3">
+      <c r="G445" s="5">
         <f>IF(AND(E445&lt;&gt;"",F445&lt;&gt;""),F445-E445,"")</f>
         <v/>
       </c>
@@ -22317,13 +22318,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E446" s="2" t="n">
+      <c r="E446" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F446" s="2" t="n">
+      <c r="F446" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G446" s="3">
+      <c r="G446" s="5">
         <f>IF(AND(E446&lt;&gt;"",F446&lt;&gt;""),F446-E446,"")</f>
         <v/>
       </c>
@@ -22369,13 +22370,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E447" s="2" t="n">
+      <c r="E447" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F447" s="2" t="n">
+      <c r="F447" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G447" s="3">
+      <c r="G447" s="5">
         <f>IF(AND(E447&lt;&gt;"",F447&lt;&gt;""),F447-E447,"")</f>
         <v/>
       </c>
@@ -22421,13 +22422,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E448" s="2" t="n">
+      <c r="E448" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F448" s="2" t="n">
+      <c r="F448" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G448" s="3">
+      <c r="G448" s="5">
         <f>IF(AND(E448&lt;&gt;"",F448&lt;&gt;""),F448-E448,"")</f>
         <v/>
       </c>
@@ -22473,13 +22474,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E449" s="2" t="n">
+      <c r="E449" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F449" s="2" t="n">
+      <c r="F449" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G449" s="3">
+      <c r="G449" s="5">
         <f>IF(AND(E449&lt;&gt;"",F449&lt;&gt;""),F449-E449,"")</f>
         <v/>
       </c>
@@ -22525,13 +22526,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E450" s="2" t="n">
+      <c r="E450" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F450" s="2" t="n">
+      <c r="F450" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G450" s="3">
+      <c r="G450" s="5">
         <f>IF(AND(E450&lt;&gt;"",F450&lt;&gt;""),F450-E450,"")</f>
         <v/>
       </c>
@@ -22577,13 +22578,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E451" s="2" t="n">
+      <c r="E451" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F451" s="2" t="n">
+      <c r="F451" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G451" s="3">
+      <c r="G451" s="5">
         <f>IF(AND(E451&lt;&gt;"",F451&lt;&gt;""),F451-E451,"")</f>
         <v/>
       </c>
@@ -22629,13 +22630,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E452" s="2" t="n">
+      <c r="E452" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F452" s="2" t="n">
+      <c r="F452" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G452" s="3">
+      <c r="G452" s="5">
         <f>IF(AND(E452&lt;&gt;"",F452&lt;&gt;""),F452-E452,"")</f>
         <v/>
       </c>
@@ -22681,13 +22682,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E453" s="2" t="n">
+      <c r="E453" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F453" s="2" t="n">
+      <c r="F453" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G453" s="3">
+      <c r="G453" s="5">
         <f>IF(AND(E453&lt;&gt;"",F453&lt;&gt;""),F453-E453,"")</f>
         <v/>
       </c>
@@ -22733,13 +22734,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E454" s="2" t="n">
+      <c r="E454" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F454" s="2" t="n">
+      <c r="F454" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G454" s="3">
+      <c r="G454" s="5">
         <f>IF(AND(E454&lt;&gt;"",F454&lt;&gt;""),F454-E454,"")</f>
         <v/>
       </c>
@@ -22785,13 +22786,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E455" s="2" t="n">
+      <c r="E455" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F455" s="2" t="n">
+      <c r="F455" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G455" s="3">
+      <c r="G455" s="5">
         <f>IF(AND(E455&lt;&gt;"",F455&lt;&gt;""),F455-E455,"")</f>
         <v/>
       </c>
@@ -22837,13 +22838,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E456" s="2" t="n">
+      <c r="E456" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F456" s="2" t="n">
+      <c r="F456" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G456" s="3">
+      <c r="G456" s="5">
         <f>IF(AND(E456&lt;&gt;"",F456&lt;&gt;""),F456-E456,"")</f>
         <v/>
       </c>
@@ -22889,13 +22890,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E457" s="2" t="n">
+      <c r="E457" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F457" s="2" t="n">
+      <c r="F457" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G457" s="3">
+      <c r="G457" s="5">
         <f>IF(AND(E457&lt;&gt;"",F457&lt;&gt;""),F457-E457,"")</f>
         <v/>
       </c>
@@ -22941,13 +22942,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E458" s="2" t="n">
+      <c r="E458" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F458" s="2" t="n">
+      <c r="F458" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G458" s="3">
+      <c r="G458" s="5">
         <f>IF(AND(E458&lt;&gt;"",F458&lt;&gt;""),F458-E458,"")</f>
         <v/>
       </c>
@@ -22993,13 +22994,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E459" s="2" t="n">
+      <c r="E459" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F459" s="2" t="n">
+      <c r="F459" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G459" s="3">
+      <c r="G459" s="5">
         <f>IF(AND(E459&lt;&gt;"",F459&lt;&gt;""),F459-E459,"")</f>
         <v/>
       </c>
@@ -23045,13 +23046,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E460" s="2" t="n">
+      <c r="E460" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F460" s="2" t="n">
+      <c r="F460" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G460" s="3">
+      <c r="G460" s="5">
         <f>IF(AND(E460&lt;&gt;"",F460&lt;&gt;""),F460-E460,"")</f>
         <v/>
       </c>
@@ -23097,13 +23098,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E461" s="2" t="n">
+      <c r="E461" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F461" s="2" t="n">
+      <c r="F461" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G461" s="3">
+      <c r="G461" s="5">
         <f>IF(AND(E461&lt;&gt;"",F461&lt;&gt;""),F461-E461,"")</f>
         <v/>
       </c>
@@ -23149,13 +23150,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E462" s="2" t="n">
+      <c r="E462" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F462" s="2" t="n">
+      <c r="F462" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G462" s="3">
+      <c r="G462" s="5">
         <f>IF(AND(E462&lt;&gt;"",F462&lt;&gt;""),F462-E462,"")</f>
         <v/>
       </c>
@@ -23201,13 +23202,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E463" s="2" t="n">
+      <c r="E463" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F463" s="2" t="n">
+      <c r="F463" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G463" s="3">
+      <c r="G463" s="5">
         <f>IF(AND(E463&lt;&gt;"",F463&lt;&gt;""),F463-E463,"")</f>
         <v/>
       </c>
@@ -23253,13 +23254,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E464" s="2" t="n">
+      <c r="E464" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F464" s="2" t="n">
+      <c r="F464" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G464" s="3">
+      <c r="G464" s="5">
         <f>IF(AND(E464&lt;&gt;"",F464&lt;&gt;""),F464-E464,"")</f>
         <v/>
       </c>
@@ -23305,13 +23306,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E465" s="2" t="n">
+      <c r="E465" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F465" s="2" t="n">
+      <c r="F465" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G465" s="3">
+      <c r="G465" s="5">
         <f>IF(AND(E465&lt;&gt;"",F465&lt;&gt;""),F465-E465,"")</f>
         <v/>
       </c>
@@ -23357,13 +23358,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E466" s="2" t="n">
+      <c r="E466" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F466" s="2" t="n">
+      <c r="F466" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G466" s="3">
+      <c r="G466" s="5">
         <f>IF(AND(E466&lt;&gt;"",F466&lt;&gt;""),F466-E466,"")</f>
         <v/>
       </c>
@@ -23409,13 +23410,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E467" s="2" t="n">
+      <c r="E467" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F467" s="2" t="n">
+      <c r="F467" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G467" s="3">
+      <c r="G467" s="5">
         <f>IF(AND(E467&lt;&gt;"",F467&lt;&gt;""),F467-E467,"")</f>
         <v/>
       </c>
@@ -23461,13 +23462,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E468" s="2" t="n">
+      <c r="E468" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F468" s="2" t="n">
+      <c r="F468" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G468" s="3">
+      <c r="G468" s="5">
         <f>IF(AND(E468&lt;&gt;"",F468&lt;&gt;""),F468-E468,"")</f>
         <v/>
       </c>
@@ -23513,13 +23514,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E469" s="2" t="n">
+      <c r="E469" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F469" s="2" t="n">
+      <c r="F469" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G469" s="3">
+      <c r="G469" s="5">
         <f>IF(AND(E469&lt;&gt;"",F469&lt;&gt;""),F469-E469,"")</f>
         <v/>
       </c>
@@ -23565,13 +23566,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E470" s="2" t="n">
+      <c r="E470" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F470" s="2" t="n">
+      <c r="F470" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G470" s="3">
+      <c r="G470" s="5">
         <f>IF(AND(E470&lt;&gt;"",F470&lt;&gt;""),F470-E470,"")</f>
         <v/>
       </c>
@@ -23617,13 +23618,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E471" s="2" t="n">
+      <c r="E471" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F471" s="2" t="n">
+      <c r="F471" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G471" s="3">
+      <c r="G471" s="5">
         <f>IF(AND(E471&lt;&gt;"",F471&lt;&gt;""),F471-E471,"")</f>
         <v/>
       </c>
@@ -23669,13 +23670,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E472" s="2" t="n">
+      <c r="E472" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F472" s="2" t="n">
+      <c r="F472" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G472" s="3">
+      <c r="G472" s="5">
         <f>IF(AND(E472&lt;&gt;"",F472&lt;&gt;""),F472-E472,"")</f>
         <v/>
       </c>
@@ -23721,13 +23722,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E473" s="2" t="n">
+      <c r="E473" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F473" s="2" t="n">
+      <c r="F473" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G473" s="3">
+      <c r="G473" s="5">
         <f>IF(AND(E473&lt;&gt;"",F473&lt;&gt;""),F473-E473,"")</f>
         <v/>
       </c>
@@ -23773,13 +23774,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E474" s="2" t="n">
+      <c r="E474" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F474" s="2" t="n">
+      <c r="F474" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G474" s="3">
+      <c r="G474" s="5">
         <f>IF(AND(E474&lt;&gt;"",F474&lt;&gt;""),F474-E474,"")</f>
         <v/>
       </c>
@@ -23825,13 +23826,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E475" s="2" t="n">
+      <c r="E475" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F475" s="2" t="n">
+      <c r="F475" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G475" s="3">
+      <c r="G475" s="5">
         <f>IF(AND(E475&lt;&gt;"",F475&lt;&gt;""),F475-E475,"")</f>
         <v/>
       </c>
@@ -23877,13 +23878,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E476" s="2" t="n">
+      <c r="E476" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F476" s="2" t="n">
+      <c r="F476" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G476" s="3">
+      <c r="G476" s="5">
         <f>IF(AND(E476&lt;&gt;"",F476&lt;&gt;""),F476-E476,"")</f>
         <v/>
       </c>
@@ -23929,13 +23930,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E477" s="2" t="n">
+      <c r="E477" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F477" s="2" t="n">
+      <c r="F477" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G477" s="3">
+      <c r="G477" s="5">
         <f>IF(AND(E477&lt;&gt;"",F477&lt;&gt;""),F477-E477,"")</f>
         <v/>
       </c>
@@ -23981,13 +23982,13 @@
           <t>Service interruption of 28 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Keningau 1, Keningau, Tambunan area, Sabah</t>
         </is>
       </c>
-      <c r="E478" s="2" t="n">
+      <c r="E478" s="4" t="n">
         <v>46226.29513888889</v>
       </c>
-      <c r="F478" s="2" t="n">
+      <c r="F478" s="4" t="n">
         <v>46226.36597222222</v>
       </c>
-      <c r="G478" s="3">
+      <c r="G478" s="5">
         <f>IF(AND(E478&lt;&gt;"",F478&lt;&gt;""),F478-E478,"")</f>
         <v/>
       </c>
@@ -24033,10 +24034,10 @@
           <t>Service interruption of 8 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E479" s="2" t="n">
+      <c r="E479" s="4" t="n">
         <v>46226.29236111111</v>
       </c>
-      <c r="G479" s="3">
+      <c r="G479" s="5">
         <f>IF(AND(E479&lt;&gt;"",F479&lt;&gt;""),F479-E479,"")</f>
         <v/>
       </c>
@@ -24072,10 +24073,10 @@
           <t>Service interruption of 8 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E480" s="2" t="n">
+      <c r="E480" s="4" t="n">
         <v>46226.29236111111</v>
       </c>
-      <c r="G480" s="3">
+      <c r="G480" s="5">
         <f>IF(AND(E480&lt;&gt;"",F480&lt;&gt;""),F480-E480,"")</f>
         <v/>
       </c>
@@ -24111,10 +24112,10 @@
           <t>Service interruption of 8 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E481" s="2" t="n">
+      <c r="E481" s="4" t="n">
         <v>46226.29236111111</v>
       </c>
-      <c r="G481" s="3">
+      <c r="G481" s="5">
         <f>IF(AND(E481&lt;&gt;"",F481&lt;&gt;""),F481-E481,"")</f>
         <v/>
       </c>
@@ -24150,10 +24151,10 @@
           <t>Service interruption of 8 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E482" s="2" t="n">
+      <c r="E482" s="4" t="n">
         <v>46226.29236111111</v>
       </c>
-      <c r="G482" s="3">
+      <c r="G482" s="5">
         <f>IF(AND(E482&lt;&gt;"",F482&lt;&gt;""),F482-E482,"")</f>
         <v/>
       </c>
@@ -24189,10 +24190,10 @@
           <t>Service interruption of 8 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E483" s="2" t="n">
+      <c r="E483" s="4" t="n">
         <v>46226.29236111111</v>
       </c>
-      <c r="G483" s="3">
+      <c r="G483" s="5">
         <f>IF(AND(E483&lt;&gt;"",F483&lt;&gt;""),F483-E483,"")</f>
         <v/>
       </c>
@@ -24228,10 +24229,10 @@
           <t>Service interruption of 8 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E484" s="2" t="n">
+      <c r="E484" s="4" t="n">
         <v>46226.29236111111</v>
       </c>
-      <c r="G484" s="3">
+      <c r="G484" s="5">
         <f>IF(AND(E484&lt;&gt;"",F484&lt;&gt;""),F484-E484,"")</f>
         <v/>
       </c>
@@ -24267,10 +24268,10 @@
           <t>Service interruption of 8 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E485" s="2" t="n">
+      <c r="E485" s="4" t="n">
         <v>46226.29236111111</v>
       </c>
-      <c r="G485" s="3">
+      <c r="G485" s="5">
         <f>IF(AND(E485&lt;&gt;"",F485&lt;&gt;""),F485-E485,"")</f>
         <v/>
       </c>
@@ -24306,10 +24307,10 @@
           <t>Service interruption of 8 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E486" s="2" t="n">
+      <c r="E486" s="4" t="n">
         <v>46226.29236111111</v>
       </c>
-      <c r="G486" s="3">
+      <c r="G486" s="5">
         <f>IF(AND(E486&lt;&gt;"",F486&lt;&gt;""),F486-E486,"")</f>
         <v/>
       </c>
@@ -24345,13 +24346,13 @@
           <t>Service interruption of 6 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E487" s="2" t="n">
+      <c r="E487" s="4" t="n">
         <v>46226.28402777778</v>
       </c>
-      <c r="F487" s="2" t="n">
+      <c r="F487" s="4" t="n">
         <v>46226.42430555556</v>
       </c>
-      <c r="G487" s="3">
+      <c r="G487" s="5">
         <f>IF(AND(E487&lt;&gt;"",F487&lt;&gt;""),F487-E487,"")</f>
         <v/>
       </c>
@@ -24397,13 +24398,13 @@
           <t>Service interruption of 6 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E488" s="2" t="n">
+      <c r="E488" s="4" t="n">
         <v>46226.28402777778</v>
       </c>
-      <c r="F488" s="2" t="n">
+      <c r="F488" s="4" t="n">
         <v>46226.42430555556</v>
       </c>
-      <c r="G488" s="3">
+      <c r="G488" s="5">
         <f>IF(AND(E488&lt;&gt;"",F488&lt;&gt;""),F488-E488,"")</f>
         <v/>
       </c>
@@ -24449,13 +24450,13 @@
           <t>Service interruption of 6 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E489" s="2" t="n">
+      <c r="E489" s="4" t="n">
         <v>46226.28402777778</v>
       </c>
-      <c r="F489" s="2" t="n">
+      <c r="F489" s="4" t="n">
         <v>46226.42430555556</v>
       </c>
-      <c r="G489" s="3">
+      <c r="G489" s="5">
         <f>IF(AND(E489&lt;&gt;"",F489&lt;&gt;""),F489-E489,"")</f>
         <v/>
       </c>
@@ -24501,13 +24502,13 @@
           <t>Service interruption of 6 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E490" s="2" t="n">
+      <c r="E490" s="4" t="n">
         <v>46226.28402777778</v>
       </c>
-      <c r="F490" s="2" t="n">
+      <c r="F490" s="4" t="n">
         <v>46226.42430555556</v>
       </c>
-      <c r="G490" s="3">
+      <c r="G490" s="5">
         <f>IF(AND(E490&lt;&gt;"",F490&lt;&gt;""),F490-E490,"")</f>
         <v/>
       </c>
@@ -24553,13 +24554,13 @@
           <t>Service interruption of 6 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E491" s="2" t="n">
+      <c r="E491" s="4" t="n">
         <v>46226.28402777778</v>
       </c>
-      <c r="F491" s="2" t="n">
+      <c r="F491" s="4" t="n">
         <v>46226.42430555556</v>
       </c>
-      <c r="G491" s="3">
+      <c r="G491" s="5">
         <f>IF(AND(E491&lt;&gt;"",F491&lt;&gt;""),F491-E491,"")</f>
         <v/>
       </c>
@@ -24605,13 +24606,13 @@
           <t>Service interruption of 6 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E492" s="2" t="n">
+      <c r="E492" s="4" t="n">
         <v>46226.28402777778</v>
       </c>
-      <c r="F492" s="2" t="n">
+      <c r="F492" s="4" t="n">
         <v>46226.42430555556</v>
       </c>
-      <c r="G492" s="3">
+      <c r="G492" s="5">
         <f>IF(AND(E492&lt;&gt;"",F492&lt;&gt;""),F492-E492,"")</f>
         <v/>
       </c>
@@ -24657,13 +24658,13 @@
           <t>Service interruption of 6 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E493" s="2" t="n">
+      <c r="E493" s="4" t="n">
         <v>46226.28402777778</v>
       </c>
-      <c r="F493" s="2" t="n">
+      <c r="F493" s="4" t="n">
         <v>46226.42430555556</v>
       </c>
-      <c r="G493" s="3">
+      <c r="G493" s="5">
         <f>IF(AND(E493&lt;&gt;"",F493&lt;&gt;""),F493-E493,"")</f>
         <v/>
       </c>
@@ -24709,13 +24710,13 @@
           <t>Service interruption of 6 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E494" s="2" t="n">
+      <c r="E494" s="4" t="n">
         <v>46226.28402777778</v>
       </c>
-      <c r="F494" s="2" t="n">
+      <c r="F494" s="4" t="n">
         <v>46226.42430555556</v>
       </c>
-      <c r="G494" s="3">
+      <c r="G494" s="5">
         <f>IF(AND(E494&lt;&gt;"",F494&lt;&gt;""),F494-E494,"")</f>
         <v/>
       </c>
@@ -24761,13 +24762,13 @@
           <t>Service interruption of 6 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E495" s="2" t="n">
+      <c r="E495" s="4" t="n">
         <v>46226.28402777778</v>
       </c>
-      <c r="F495" s="2" t="n">
+      <c r="F495" s="4" t="n">
         <v>46226.42430555556</v>
       </c>
-      <c r="G495" s="3">
+      <c r="G495" s="5">
         <f>IF(AND(E495&lt;&gt;"",F495&lt;&gt;""),F495-E495,"")</f>
         <v/>
       </c>
@@ -24813,13 +24814,13 @@
           <t>Service interruption of 6 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E496" s="2" t="n">
+      <c r="E496" s="4" t="n">
         <v>46226.28402777778</v>
       </c>
-      <c r="F496" s="2" t="n">
+      <c r="F496" s="4" t="n">
         <v>46226.42430555556</v>
       </c>
-      <c r="G496" s="3">
+      <c r="G496" s="5">
         <f>IF(AND(E496&lt;&gt;"",F496&lt;&gt;""),F496-E496,"")</f>
         <v/>
       </c>
@@ -24865,13 +24866,13 @@
           <t>Service interruption of 6 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Bau / Lundu / Sematan area, Sarawak</t>
         </is>
       </c>
-      <c r="E497" s="2" t="n">
+      <c r="E497" s="4" t="n">
         <v>46226.28402777778</v>
       </c>
-      <c r="F497" s="2" t="n">
+      <c r="F497" s="4" t="n">
         <v>46226.42430555556</v>
       </c>
-      <c r="G497" s="3">
+      <c r="G497" s="5">
         <f>IF(AND(E497&lt;&gt;"",F497&lt;&gt;""),F497-E497,"")</f>
         <v/>
       </c>
@@ -24917,10 +24918,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Ranau area, Sabah</t>
         </is>
       </c>
-      <c r="E498" s="2" t="n">
+      <c r="E498" s="4" t="n">
         <v>46226.28194444445</v>
       </c>
-      <c r="G498" s="3">
+      <c r="G498" s="5">
         <f>IF(AND(E498&lt;&gt;"",F498&lt;&gt;""),F498-E498,"")</f>
         <v/>
       </c>
@@ -24951,10 +24952,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Ranau area, Sabah</t>
         </is>
       </c>
-      <c r="E499" s="2" t="n">
+      <c r="E499" s="4" t="n">
         <v>46226.28194444445</v>
       </c>
-      <c r="G499" s="3">
+      <c r="G499" s="5">
         <f>IF(AND(E499&lt;&gt;"",F499&lt;&gt;""),F499-E499,"")</f>
         <v/>
       </c>
@@ -24985,10 +24986,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Ranau area, Sabah</t>
         </is>
       </c>
-      <c r="E500" s="2" t="n">
+      <c r="E500" s="4" t="n">
         <v>46226.28194444445</v>
       </c>
-      <c r="G500" s="3">
+      <c r="G500" s="5">
         <f>IF(AND(E500&lt;&gt;"",F500&lt;&gt;""),F500-E500,"")</f>
         <v/>
       </c>
@@ -25019,10 +25020,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Ranau area, Sabah</t>
         </is>
       </c>
-      <c r="E501" s="2" t="n">
+      <c r="E501" s="4" t="n">
         <v>46226.28194444445</v>
       </c>
-      <c r="G501" s="3">
+      <c r="G501" s="5">
         <f>IF(AND(E501&lt;&gt;"",F501&lt;&gt;""),F501-E501,"")</f>
         <v/>
       </c>
@@ -25053,10 +25054,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Ranau area, Sabah</t>
         </is>
       </c>
-      <c r="E502" s="2" t="n">
+      <c r="E502" s="4" t="n">
         <v>46226.28194444445</v>
       </c>
-      <c r="G502" s="3">
+      <c r="G502" s="5">
         <f>IF(AND(E502&lt;&gt;"",F502&lt;&gt;""),F502-E502,"")</f>
         <v/>
       </c>
@@ -25087,10 +25088,10 @@
           <t>Service interruption of 6 (2G)(4G) xD sites at certain parts of Ranau area, Sabah</t>
         </is>
       </c>
-      <c r="E503" s="2" t="n">
+      <c r="E503" s="4" t="n">
         <v>46226.28194444445</v>
       </c>
-      <c r="G503" s="3">
+      <c r="G503" s="5">
         <f>IF(AND(E503&lt;&gt;"",F503&lt;&gt;""),F503-E503,"")</f>
         <v/>
       </c>
@@ -25126,13 +25127,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E504" s="2" t="n">
+      <c r="E504" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F504" s="2" t="n">
+      <c r="F504" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G504" s="3">
+      <c r="G504" s="5">
         <f>IF(AND(E504&lt;&gt;"",F504&lt;&gt;""),F504-E504,"")</f>
         <v/>
       </c>
@@ -25178,13 +25179,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E505" s="2" t="n">
+      <c r="E505" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F505" s="2" t="n">
+      <c r="F505" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G505" s="3">
+      <c r="G505" s="5">
         <f>IF(AND(E505&lt;&gt;"",F505&lt;&gt;""),F505-E505,"")</f>
         <v/>
       </c>
@@ -25230,13 +25231,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E506" s="2" t="n">
+      <c r="E506" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F506" s="2" t="n">
+      <c r="F506" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G506" s="3">
+      <c r="G506" s="5">
         <f>IF(AND(E506&lt;&gt;"",F506&lt;&gt;""),F506-E506,"")</f>
         <v/>
       </c>
@@ -25282,13 +25283,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E507" s="2" t="n">
+      <c r="E507" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F507" s="2" t="n">
+      <c r="F507" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G507" s="3">
+      <c r="G507" s="5">
         <f>IF(AND(E507&lt;&gt;"",F507&lt;&gt;""),F507-E507,"")</f>
         <v/>
       </c>
@@ -25334,13 +25335,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E508" s="2" t="n">
+      <c r="E508" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F508" s="2" t="n">
+      <c r="F508" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G508" s="3">
+      <c r="G508" s="5">
         <f>IF(AND(E508&lt;&gt;"",F508&lt;&gt;""),F508-E508,"")</f>
         <v/>
       </c>
@@ -25386,13 +25387,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E509" s="2" t="n">
+      <c r="E509" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F509" s="2" t="n">
+      <c r="F509" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G509" s="3">
+      <c r="G509" s="5">
         <f>IF(AND(E509&lt;&gt;"",F509&lt;&gt;""),F509-E509,"")</f>
         <v/>
       </c>
@@ -25438,13 +25439,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E510" s="2" t="n">
+      <c r="E510" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F510" s="2" t="n">
+      <c r="F510" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G510" s="3">
+      <c r="G510" s="5">
         <f>IF(AND(E510&lt;&gt;"",F510&lt;&gt;""),F510-E510,"")</f>
         <v/>
       </c>
@@ -25490,13 +25491,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E511" s="2" t="n">
+      <c r="E511" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F511" s="2" t="n">
+      <c r="F511" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G511" s="3">
+      <c r="G511" s="5">
         <f>IF(AND(E511&lt;&gt;"",F511&lt;&gt;""),F511-E511,"")</f>
         <v/>
       </c>
@@ -25542,13 +25543,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E512" s="2" t="n">
+      <c r="E512" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F512" s="2" t="n">
+      <c r="F512" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G512" s="3">
+      <c r="G512" s="5">
         <f>IF(AND(E512&lt;&gt;"",F512&lt;&gt;""),F512-E512,"")</f>
         <v/>
       </c>
@@ -25594,13 +25595,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E513" s="2" t="n">
+      <c r="E513" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F513" s="2" t="n">
+      <c r="F513" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G513" s="3">
+      <c r="G513" s="5">
         <f>IF(AND(E513&lt;&gt;"",F513&lt;&gt;""),F513-E513,"")</f>
         <v/>
       </c>
@@ -25646,13 +25647,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E514" s="2" t="n">
+      <c r="E514" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F514" s="2" t="n">
+      <c r="F514" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G514" s="3">
+      <c r="G514" s="5">
         <f>IF(AND(E514&lt;&gt;"",F514&lt;&gt;""),F514-E514,"")</f>
         <v/>
       </c>
@@ -25698,13 +25699,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E515" s="2" t="n">
+      <c r="E515" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F515" s="2" t="n">
+      <c r="F515" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G515" s="3">
+      <c r="G515" s="5">
         <f>IF(AND(E515&lt;&gt;"",F515&lt;&gt;""),F515-E515,"")</f>
         <v/>
       </c>
@@ -25750,13 +25751,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E516" s="2" t="n">
+      <c r="E516" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F516" s="2" t="n">
+      <c r="F516" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G516" s="3">
+      <c r="G516" s="5">
         <f>IF(AND(E516&lt;&gt;"",F516&lt;&gt;""),F516-E516,"")</f>
         <v/>
       </c>
@@ -25802,13 +25803,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E517" s="2" t="n">
+      <c r="E517" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F517" s="2" t="n">
+      <c r="F517" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G517" s="3">
+      <c r="G517" s="5">
         <f>IF(AND(E517&lt;&gt;"",F517&lt;&gt;""),F517-E517,"")</f>
         <v/>
       </c>
@@ -25854,13 +25855,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E518" s="2" t="n">
+      <c r="E518" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F518" s="2" t="n">
+      <c r="F518" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G518" s="3">
+      <c r="G518" s="5">
         <f>IF(AND(E518&lt;&gt;"",F518&lt;&gt;""),F518-E518,"")</f>
         <v/>
       </c>
@@ -25906,13 +25907,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E519" s="2" t="n">
+      <c r="E519" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F519" s="2" t="n">
+      <c r="F519" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G519" s="3">
+      <c r="G519" s="5">
         <f>IF(AND(E519&lt;&gt;"",F519&lt;&gt;""),F519-E519,"")</f>
         <v/>
       </c>
@@ -25958,13 +25959,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E520" s="2" t="n">
+      <c r="E520" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F520" s="2" t="n">
+      <c r="F520" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G520" s="3">
+      <c r="G520" s="5">
         <f>IF(AND(E520&lt;&gt;"",F520&lt;&gt;""),F520-E520,"")</f>
         <v/>
       </c>
@@ -26010,13 +26011,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 9 (2G)(4G) xC sites at certain parts of Damansara, TTDI, Bandar Utama area, Selangor, Wp Kuala Lumpur</t>
         </is>
       </c>
-      <c r="E521" s="2" t="n">
+      <c r="E521" s="4" t="n">
         <v>46226.2125</v>
       </c>
-      <c r="F521" s="2" t="n">
+      <c r="F521" s="4" t="n">
         <v>46226.54236111111</v>
       </c>
-      <c r="G521" s="3">
+      <c r="G521" s="5">
         <f>IF(AND(E521&lt;&gt;"",F521&lt;&gt;""),F521-E521,"")</f>
         <v/>
       </c>
@@ -26057,10 +26058,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Jerantut area, Pahang</t>
         </is>
       </c>
-      <c r="E522" s="2" t="n">
+      <c r="E522" s="4" t="n">
         <v>46226.20694444444</v>
       </c>
-      <c r="G522" s="3">
+      <c r="G522" s="5">
         <f>IF(AND(E522&lt;&gt;"",F522&lt;&gt;""),F522-E522,"")</f>
         <v/>
       </c>
@@ -26091,10 +26092,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Jerantut area, Pahang</t>
         </is>
       </c>
-      <c r="E523" s="2" t="n">
+      <c r="E523" s="4" t="n">
         <v>46226.20694444444</v>
       </c>
-      <c r="G523" s="3">
+      <c r="G523" s="5">
         <f>IF(AND(E523&lt;&gt;"",F523&lt;&gt;""),F523-E523,"")</f>
         <v/>
       </c>
@@ -26125,10 +26126,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Jerantut area, Pahang</t>
         </is>
       </c>
-      <c r="E524" s="2" t="n">
+      <c r="E524" s="4" t="n">
         <v>46226.20694444444</v>
       </c>
-      <c r="G524" s="3">
+      <c r="G524" s="5">
         <f>IF(AND(E524&lt;&gt;"",F524&lt;&gt;""),F524-E524,"")</f>
         <v/>
       </c>
@@ -26164,10 +26165,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Jerantut area, Pahang</t>
         </is>
       </c>
-      <c r="E525" s="2" t="n">
+      <c r="E525" s="4" t="n">
         <v>46226.20694444444</v>
       </c>
-      <c r="G525" s="3">
+      <c r="G525" s="5">
         <f>IF(AND(E525&lt;&gt;"",F525&lt;&gt;""),F525-E525,"")</f>
         <v/>
       </c>
@@ -26203,10 +26204,10 @@
           <t>Service interruption of 3 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Jerantut area, Pahang</t>
         </is>
       </c>
-      <c r="E526" s="2" t="n">
+      <c r="E526" s="4" t="n">
         <v>46226.20694444444</v>
       </c>
-      <c r="G526" s="3">
+      <c r="G526" s="5">
         <f>IF(AND(E526&lt;&gt;"",F526&lt;&gt;""),F526-E526,"")</f>
         <v/>
       </c>
@@ -26242,10 +26243,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Kota Tinggi, Kota Tinggi 1 area, Johor</t>
         </is>
       </c>
-      <c r="E527" s="2" t="n">
+      <c r="E527" s="4" t="n">
         <v>46226.19791666666</v>
       </c>
-      <c r="G527" s="3">
+      <c r="G527" s="5">
         <f>IF(AND(E527&lt;&gt;"",F527&lt;&gt;""),F527-E527,"")</f>
         <v/>
       </c>
@@ -26276,10 +26277,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Kota Tinggi, Kota Tinggi 1 area, Johor</t>
         </is>
       </c>
-      <c r="E528" s="2" t="n">
+      <c r="E528" s="4" t="n">
         <v>46226.19791666666</v>
       </c>
-      <c r="G528" s="3">
+      <c r="G528" s="5">
         <f>IF(AND(E528&lt;&gt;"",F528&lt;&gt;""),F528-E528,"")</f>
         <v/>
       </c>
@@ -26310,10 +26311,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Kota Tinggi, Kota Tinggi 1 area, Johor</t>
         </is>
       </c>
-      <c r="E529" s="2" t="n">
+      <c r="E529" s="4" t="n">
         <v>46226.19791666666</v>
       </c>
-      <c r="G529" s="3">
+      <c r="G529" s="5">
         <f>IF(AND(E529&lt;&gt;"",F529&lt;&gt;""),F529-E529,"")</f>
         <v/>
       </c>
@@ -26344,10 +26345,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Kota Tinggi, Kota Tinggi 1 area, Johor</t>
         </is>
       </c>
-      <c r="E530" s="2" t="n">
+      <c r="E530" s="4" t="n">
         <v>46226.19791666666</v>
       </c>
-      <c r="G530" s="3">
+      <c r="G530" s="5">
         <f>IF(AND(E530&lt;&gt;"",F530&lt;&gt;""),F530-E530,"")</f>
         <v/>
       </c>
@@ -26383,10 +26384,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Kota Tinggi, Kota Tinggi 1 area, Johor</t>
         </is>
       </c>
-      <c r="E531" s="2" t="n">
+      <c r="E531" s="4" t="n">
         <v>46226.19791666666</v>
       </c>
-      <c r="G531" s="3">
+      <c r="G531" s="5">
         <f>IF(AND(E531&lt;&gt;"",F531&lt;&gt;""),F531-E531,"")</f>
         <v/>
       </c>
@@ -26422,10 +26423,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Kota Tinggi, Kota Tinggi 1 area, Johor</t>
         </is>
       </c>
-      <c r="E532" s="2" t="n">
+      <c r="E532" s="4" t="n">
         <v>46226.19791666666</v>
       </c>
-      <c r="G532" s="3">
+      <c r="G532" s="5">
         <f>IF(AND(E532&lt;&gt;"",F532&lt;&gt;""),F532-E532,"")</f>
         <v/>
       </c>
@@ -26461,10 +26462,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Kota Tinggi, Kota Tinggi 1 area, Johor</t>
         </is>
       </c>
-      <c r="E533" s="2" t="n">
+      <c r="E533" s="4" t="n">
         <v>46226.19791666666</v>
       </c>
-      <c r="G533" s="3">
+      <c r="G533" s="5">
         <f>IF(AND(E533&lt;&gt;"",F533&lt;&gt;""),F533-E533,"")</f>
         <v/>
       </c>
@@ -26500,10 +26501,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Kota Tinggi, Kota Tinggi 1 area, Johor</t>
         </is>
       </c>
-      <c r="E534" s="2" t="n">
+      <c r="E534" s="4" t="n">
         <v>46226.19791666666</v>
       </c>
-      <c r="G534" s="3">
+      <c r="G534" s="5">
         <f>IF(AND(E534&lt;&gt;"",F534&lt;&gt;""),F534-E534,"")</f>
         <v/>
       </c>
@@ -26534,10 +26535,10 @@
           <t>Service interruption of 4 (2G)(4G) xD and 4 (2G)(4G) xC sites at certain parts of Kota Tinggi, Kota Tinggi 1 area, Johor</t>
         </is>
       </c>
-      <c r="E535" s="2" t="n">
+      <c r="E535" s="4" t="n">
         <v>46226.19791666666</v>
       </c>
-      <c r="G535" s="3">
+      <c r="G535" s="5">
         <f>IF(AND(E535&lt;&gt;"",F535&lt;&gt;""),F535-E535,"")</f>
         <v/>
       </c>
@@ -26573,10 +26574,10 @@
           <t>Service interruption of 5 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E536" s="2" t="n">
+      <c r="E536" s="4" t="n">
         <v>46226.17777777778</v>
       </c>
-      <c r="G536" s="3">
+      <c r="G536" s="5">
         <f>IF(AND(E536&lt;&gt;"",F536&lt;&gt;""),F536-E536,"")</f>
         <v/>
       </c>
@@ -26612,10 +26613,10 @@
           <t>Service interruption of 5 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E537" s="2" t="n">
+      <c r="E537" s="4" t="n">
         <v>46226.17777777778</v>
       </c>
-      <c r="G537" s="3">
+      <c r="G537" s="5">
         <f>IF(AND(E537&lt;&gt;"",F537&lt;&gt;""),F537-E537,"")</f>
         <v/>
       </c>
@@ -26651,10 +26652,10 @@
           <t>Service interruption of 5 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E538" s="2" t="n">
+      <c r="E538" s="4" t="n">
         <v>46226.17777777778</v>
       </c>
-      <c r="G538" s="3">
+      <c r="G538" s="5">
         <f>IF(AND(E538&lt;&gt;"",F538&lt;&gt;""),F538-E538,"")</f>
         <v/>
       </c>
@@ -26690,10 +26691,10 @@
           <t>Service interruption of 5 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E539" s="2" t="n">
+      <c r="E539" s="4" t="n">
         <v>46226.17777777778</v>
       </c>
-      <c r="G539" s="3">
+      <c r="G539" s="5">
         <f>IF(AND(E539&lt;&gt;"",F539&lt;&gt;""),F539-E539,"")</f>
         <v/>
       </c>
@@ -26729,10 +26730,10 @@
           <t>Service interruption of 5 (2G)(4G) xC sites at certain parts of Sandakan - Telupid area, Sabah</t>
         </is>
       </c>
-      <c r="E540" s="2" t="n">
+      <c r="E540" s="4" t="n">
         <v>46226.17777777778</v>
       </c>
-      <c r="G540" s="3">
+      <c r="G540" s="5">
         <f>IF(AND(E540&lt;&gt;"",F540&lt;&gt;""),F540-E540,"")</f>
         <v/>
       </c>
@@ -26768,10 +26769,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Limbang / Lawas area, Sarawak</t>
         </is>
       </c>
-      <c r="E541" s="2" t="n">
+      <c r="E541" s="4" t="n">
         <v>46226.13958333333</v>
       </c>
-      <c r="G541" s="3">
+      <c r="G541" s="5">
         <f>IF(AND(E541&lt;&gt;"",F541&lt;&gt;""),F541-E541,"")</f>
         <v/>
       </c>
@@ -26807,10 +26808,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Limbang / Lawas area, Sarawak</t>
         </is>
       </c>
-      <c r="E542" s="2" t="n">
+      <c r="E542" s="4" t="n">
         <v>46226.13958333333</v>
       </c>
-      <c r="G542" s="3">
+      <c r="G542" s="5">
         <f>IF(AND(E542&lt;&gt;"",F542&lt;&gt;""),F542-E542,"")</f>
         <v/>
       </c>
@@ -26841,10 +26842,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Limbang / Lawas area, Sarawak</t>
         </is>
       </c>
-      <c r="E543" s="2" t="n">
+      <c r="E543" s="4" t="n">
         <v>46226.13958333333</v>
       </c>
-      <c r="G543" s="3">
+      <c r="G543" s="5">
         <f>IF(AND(E543&lt;&gt;"",F543&lt;&gt;""),F543-E543,"")</f>
         <v/>
       </c>
@@ -26875,10 +26876,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Limbang / Lawas area, Sarawak</t>
         </is>
       </c>
-      <c r="E544" s="2" t="n">
+      <c r="E544" s="4" t="n">
         <v>46226.13958333333</v>
       </c>
-      <c r="G544" s="3">
+      <c r="G544" s="5">
         <f>IF(AND(E544&lt;&gt;"",F544&lt;&gt;""),F544-E544,"")</f>
         <v/>
       </c>
@@ -26914,10 +26915,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Limbang / Lawas area, Sarawak</t>
         </is>
       </c>
-      <c r="E545" s="2" t="n">
+      <c r="E545" s="4" t="n">
         <v>46226.13958333333</v>
       </c>
-      <c r="G545" s="3">
+      <c r="G545" s="5">
         <f>IF(AND(E545&lt;&gt;"",F545&lt;&gt;""),F545-E545,"")</f>
         <v/>
       </c>
@@ -26953,10 +26954,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Limbang / Lawas area, Sarawak</t>
         </is>
       </c>
-      <c r="E546" s="2" t="n">
+      <c r="E546" s="4" t="n">
         <v>46226.13958333333</v>
       </c>
-      <c r="G546" s="3">
+      <c r="G546" s="5">
         <f>IF(AND(E546&lt;&gt;"",F546&lt;&gt;""),F546-E546,"")</f>
         <v/>
       </c>
@@ -26992,10 +26993,10 @@
           <t>Service interruption of 2 (2G)(4G) xD and 5 (2G)(4G) xC sites at certain parts of Limbang / Lawas area, Sarawak</t>
         </is>
       </c>
-      <c r="E547" s="2" t="n">
+      <c r="E547" s="4" t="n">
         <v>46226.13958333333</v>
       </c>
-      <c r="G547" s="3">
+      <c r="G547" s="5">
         <f>IF(AND(E547&lt;&gt;"",F547&lt;&gt;""),F547-E547,"")</f>
         <v/>
       </c>
@@ -27031,13 +27032,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sibu 6, Mukah / Matu Daro area, Sarawak</t>
         </is>
       </c>
-      <c r="E548" s="2" t="n">
+      <c r="E548" s="4" t="n">
         <v>46226.02430555555</v>
       </c>
-      <c r="F548" s="2" t="n">
+      <c r="F548" s="4" t="n">
         <v>46226.05208333334</v>
       </c>
-      <c r="G548" s="3">
+      <c r="G548" s="5">
         <f>IF(AND(E548&lt;&gt;"",F548&lt;&gt;""),F548-E548,"")</f>
         <v/>
       </c>
@@ -27083,13 +27084,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sibu 6, Mukah / Matu Daro area, Sarawak</t>
         </is>
       </c>
-      <c r="E549" s="2" t="n">
+      <c r="E549" s="4" t="n">
         <v>46226.02430555555</v>
       </c>
-      <c r="F549" s="2" t="n">
+      <c r="F549" s="4" t="n">
         <v>46226.05208333334</v>
       </c>
-      <c r="G549" s="3">
+      <c r="G549" s="5">
         <f>IF(AND(E549&lt;&gt;"",F549&lt;&gt;""),F549-E549,"")</f>
         <v/>
       </c>
@@ -27135,13 +27136,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sibu 6, Mukah / Matu Daro area, Sarawak</t>
         </is>
       </c>
-      <c r="E550" s="2" t="n">
+      <c r="E550" s="4" t="n">
         <v>46226.02430555555</v>
       </c>
-      <c r="F550" s="2" t="n">
+      <c r="F550" s="4" t="n">
         <v>46226.05208333334</v>
       </c>
-      <c r="G550" s="3">
+      <c r="G550" s="5">
         <f>IF(AND(E550&lt;&gt;"",F550&lt;&gt;""),F550-E550,"")</f>
         <v/>
       </c>
@@ -27187,13 +27188,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sibu 6, Mukah / Matu Daro area, Sarawak</t>
         </is>
       </c>
-      <c r="E551" s="2" t="n">
+      <c r="E551" s="4" t="n">
         <v>46226.02430555555</v>
       </c>
-      <c r="F551" s="2" t="n">
+      <c r="F551" s="4" t="n">
         <v>46226.05208333334</v>
       </c>
-      <c r="G551" s="3">
+      <c r="G551" s="5">
         <f>IF(AND(E551&lt;&gt;"",F551&lt;&gt;""),F551-E551,"")</f>
         <v/>
       </c>
@@ -27239,13 +27240,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sibu 6, Mukah / Matu Daro area, Sarawak</t>
         </is>
       </c>
-      <c r="E552" s="2" t="n">
+      <c r="E552" s="4" t="n">
         <v>46226.02430555555</v>
       </c>
-      <c r="F552" s="2" t="n">
+      <c r="F552" s="4" t="n">
         <v>46226.05208333334</v>
       </c>
-      <c r="G552" s="3">
+      <c r="G552" s="5">
         <f>IF(AND(E552&lt;&gt;"",F552&lt;&gt;""),F552-E552,"")</f>
         <v/>
       </c>
@@ -27291,13 +27292,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sibu 6, Mukah / Matu Daro area, Sarawak</t>
         </is>
       </c>
-      <c r="E553" s="2" t="n">
+      <c r="E553" s="4" t="n">
         <v>46226.02430555555</v>
       </c>
-      <c r="F553" s="2" t="n">
+      <c r="F553" s="4" t="n">
         <v>46226.05208333334</v>
       </c>
-      <c r="G553" s="3">
+      <c r="G553" s="5">
         <f>IF(AND(E553&lt;&gt;"",F553&lt;&gt;""),F553-E553,"")</f>
         <v/>
       </c>
@@ -27343,13 +27344,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sibu 6, Mukah / Matu Daro area, Sarawak</t>
         </is>
       </c>
-      <c r="E554" s="2" t="n">
+      <c r="E554" s="4" t="n">
         <v>46226.02430555555</v>
       </c>
-      <c r="F554" s="2" t="n">
+      <c r="F554" s="4" t="n">
         <v>46226.05208333334</v>
       </c>
-      <c r="G554" s="3">
+      <c r="G554" s="5">
         <f>IF(AND(E554&lt;&gt;"",F554&lt;&gt;""),F554-E554,"")</f>
         <v/>
       </c>
@@ -27395,13 +27396,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sibu 6, Mukah / Matu Daro area, Sarawak</t>
         </is>
       </c>
-      <c r="E555" s="2" t="n">
+      <c r="E555" s="4" t="n">
         <v>46226.02430555555</v>
       </c>
-      <c r="F555" s="2" t="n">
+      <c r="F555" s="4" t="n">
         <v>46226.05208333334</v>
       </c>
-      <c r="G555" s="3">
+      <c r="G555" s="5">
         <f>IF(AND(E555&lt;&gt;"",F555&lt;&gt;""),F555-E555,"")</f>
         <v/>
       </c>
@@ -27447,13 +27448,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sibu 6, Mukah / Matu Daro area, Sarawak</t>
         </is>
       </c>
-      <c r="E556" s="2" t="n">
+      <c r="E556" s="4" t="n">
         <v>46226.02430555555</v>
       </c>
-      <c r="F556" s="2" t="n">
+      <c r="F556" s="4" t="n">
         <v>46226.05208333334</v>
       </c>
-      <c r="G556" s="3">
+      <c r="G556" s="5">
         <f>IF(AND(E556&lt;&gt;"",F556&lt;&gt;""),F556-E556,"")</f>
         <v/>
       </c>
@@ -27499,13 +27500,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sibu 6, Mukah / Matu Daro area, Sarawak</t>
         </is>
       </c>
-      <c r="E557" s="2" t="n">
+      <c r="E557" s="4" t="n">
         <v>46226.02430555555</v>
       </c>
-      <c r="F557" s="2" t="n">
+      <c r="F557" s="4" t="n">
         <v>46226.05208333334</v>
       </c>
-      <c r="G557" s="3">
+      <c r="G557" s="5">
         <f>IF(AND(E557&lt;&gt;"",F557&lt;&gt;""),F557-E557,"")</f>
         <v/>
       </c>
@@ -27551,13 +27552,13 @@
           <t>Service interruption of 9 (2G)(4G) xD and 2 (2G)(4G) xC sites at certain parts of Sibu 6, Mukah / Matu Daro area, Sarawak</t>
         </is>
       </c>
-      <c r="E558" s="2" t="n">
+      <c r="E558" s="4" t="n">
         <v>46226.02430555555</v>
       </c>
-      <c r="F558" s="2" t="n">
+      <c r="F558" s="4" t="n">
         <v>46226.05208333334</v>
       </c>
-      <c r="G558" s="3">
+      <c r="G558" s="5">
         <f>IF(AND(E558&lt;&gt;"",F558&lt;&gt;""),F558-E558,"")</f>
         <v/>
       </c>
@@ -27603,10 +27604,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E559" s="2" t="n">
+      <c r="E559" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G559" s="3">
+      <c r="G559" s="5">
         <f>IF(AND(E559&lt;&gt;"",F559&lt;&gt;""),F559-E559,"")</f>
         <v/>
       </c>
@@ -27652,10 +27653,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E560" s="2" t="n">
+      <c r="E560" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G560" s="3">
+      <c r="G560" s="5">
         <f>IF(AND(E560&lt;&gt;"",F560&lt;&gt;""),F560-E560,"")</f>
         <v/>
       </c>
@@ -27701,10 +27702,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E561" s="2" t="n">
+      <c r="E561" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G561" s="3">
+      <c r="G561" s="5">
         <f>IF(AND(E561&lt;&gt;"",F561&lt;&gt;""),F561-E561,"")</f>
         <v/>
       </c>
@@ -27750,10 +27751,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E562" s="2" t="n">
+      <c r="E562" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G562" s="3">
+      <c r="G562" s="5">
         <f>IF(AND(E562&lt;&gt;"",F562&lt;&gt;""),F562-E562,"")</f>
         <v/>
       </c>
@@ -27799,10 +27800,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E563" s="2" t="n">
+      <c r="E563" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G563" s="3">
+      <c r="G563" s="5">
         <f>IF(AND(E563&lt;&gt;"",F563&lt;&gt;""),F563-E563,"")</f>
         <v/>
       </c>
@@ -27848,10 +27849,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E564" s="2" t="n">
+      <c r="E564" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G564" s="3">
+      <c r="G564" s="5">
         <f>IF(AND(E564&lt;&gt;"",F564&lt;&gt;""),F564-E564,"")</f>
         <v/>
       </c>
@@ -27897,10 +27898,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E565" s="2" t="n">
+      <c r="E565" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G565" s="3">
+      <c r="G565" s="5">
         <f>IF(AND(E565&lt;&gt;"",F565&lt;&gt;""),F565-E565,"")</f>
         <v/>
       </c>
@@ -27946,10 +27947,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E566" s="2" t="n">
+      <c r="E566" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G566" s="3">
+      <c r="G566" s="5">
         <f>IF(AND(E566&lt;&gt;"",F566&lt;&gt;""),F566-E566,"")</f>
         <v/>
       </c>
@@ -27995,10 +27996,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E567" s="2" t="n">
+      <c r="E567" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G567" s="3">
+      <c r="G567" s="5">
         <f>IF(AND(E567&lt;&gt;"",F567&lt;&gt;""),F567-E567,"")</f>
         <v/>
       </c>
@@ -28044,10 +28045,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E568" s="2" t="n">
+      <c r="E568" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G568" s="3">
+      <c r="G568" s="5">
         <f>IF(AND(E568&lt;&gt;"",F568&lt;&gt;""),F568-E568,"")</f>
         <v/>
       </c>
@@ -28093,10 +28094,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E569" s="2" t="n">
+      <c r="E569" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G569" s="3">
+      <c r="G569" s="5">
         <f>IF(AND(E569&lt;&gt;"",F569&lt;&gt;""),F569-E569,"")</f>
         <v/>
       </c>
@@ -28142,10 +28143,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E570" s="2" t="n">
+      <c r="E570" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G570" s="3">
+      <c r="G570" s="5">
         <f>IF(AND(E570&lt;&gt;"",F570&lt;&gt;""),F570-E570,"")</f>
         <v/>
       </c>
@@ -28191,10 +28192,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E571" s="2" t="n">
+      <c r="E571" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G571" s="3">
+      <c r="G571" s="5">
         <f>IF(AND(E571&lt;&gt;"",F571&lt;&gt;""),F571-E571,"")</f>
         <v/>
       </c>
@@ -28240,10 +28241,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E572" s="2" t="n">
+      <c r="E572" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G572" s="3">
+      <c r="G572" s="5">
         <f>IF(AND(E572&lt;&gt;"",F572&lt;&gt;""),F572-E572,"")</f>
         <v/>
       </c>
@@ -28289,10 +28290,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E573" s="2" t="n">
+      <c r="E573" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G573" s="3">
+      <c r="G573" s="5">
         <f>IF(AND(E573&lt;&gt;"",F573&lt;&gt;""),F573-E573,"")</f>
         <v/>
       </c>
@@ -28338,10 +28339,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E574" s="2" t="n">
+      <c r="E574" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G574" s="3">
+      <c r="G574" s="5">
         <f>IF(AND(E574&lt;&gt;"",F574&lt;&gt;""),F574-E574,"")</f>
         <v/>
       </c>
@@ -28387,10 +28388,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E575" s="2" t="n">
+      <c r="E575" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G575" s="3">
+      <c r="G575" s="5">
         <f>IF(AND(E575&lt;&gt;"",F575&lt;&gt;""),F575-E575,"")</f>
         <v/>
       </c>
@@ -28436,10 +28437,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E576" s="2" t="n">
+      <c r="E576" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G576" s="3">
+      <c r="G576" s="5">
         <f>IF(AND(E576&lt;&gt;"",F576&lt;&gt;""),F576-E576,"")</f>
         <v/>
       </c>
@@ -28485,10 +28486,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E577" s="2" t="n">
+      <c r="E577" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G577" s="3">
+      <c r="G577" s="5">
         <f>IF(AND(E577&lt;&gt;"",F577&lt;&gt;""),F577-E577,"")</f>
         <v/>
       </c>
@@ -28534,10 +28535,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E578" s="2" t="n">
+      <c r="E578" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G578" s="3">
+      <c r="G578" s="5">
         <f>IF(AND(E578&lt;&gt;"",F578&lt;&gt;""),F578-E578,"")</f>
         <v/>
       </c>
@@ -28583,10 +28584,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E579" s="2" t="n">
+      <c r="E579" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G579" s="3">
+      <c r="G579" s="5">
         <f>IF(AND(E579&lt;&gt;"",F579&lt;&gt;""),F579-E579,"")</f>
         <v/>
       </c>
@@ -28632,10 +28633,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E580" s="2" t="n">
+      <c r="E580" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G580" s="3">
+      <c r="G580" s="5">
         <f>IF(AND(E580&lt;&gt;"",F580&lt;&gt;""),F580-E580,"")</f>
         <v/>
       </c>
@@ -28681,10 +28682,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E581" s="2" t="n">
+      <c r="E581" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G581" s="3">
+      <c r="G581" s="5">
         <f>IF(AND(E581&lt;&gt;"",F581&lt;&gt;""),F581-E581,"")</f>
         <v/>
       </c>
@@ -28730,10 +28731,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E582" s="2" t="n">
+      <c r="E582" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G582" s="3">
+      <c r="G582" s="5">
         <f>IF(AND(E582&lt;&gt;"",F582&lt;&gt;""),F582-E582,"")</f>
         <v/>
       </c>
@@ -28779,10 +28780,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E583" s="2" t="n">
+      <c r="E583" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G583" s="3">
+      <c r="G583" s="5">
         <f>IF(AND(E583&lt;&gt;"",F583&lt;&gt;""),F583-E583,"")</f>
         <v/>
       </c>
@@ -28828,10 +28829,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E584" s="2" t="n">
+      <c r="E584" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G584" s="3">
+      <c r="G584" s="5">
         <f>IF(AND(E584&lt;&gt;"",F584&lt;&gt;""),F584-E584,"")</f>
         <v/>
       </c>
@@ -28877,10 +28878,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E585" s="2" t="n">
+      <c r="E585" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G585" s="3">
+      <c r="G585" s="5">
         <f>IF(AND(E585&lt;&gt;"",F585&lt;&gt;""),F585-E585,"")</f>
         <v/>
       </c>
@@ -28926,10 +28927,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E586" s="2" t="n">
+      <c r="E586" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G586" s="3">
+      <c r="G586" s="5">
         <f>IF(AND(E586&lt;&gt;"",F586&lt;&gt;""),F586-E586,"")</f>
         <v/>
       </c>
@@ -28975,10 +28976,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E587" s="2" t="n">
+      <c r="E587" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G587" s="3">
+      <c r="G587" s="5">
         <f>IF(AND(E587&lt;&gt;"",F587&lt;&gt;""),F587-E587,"")</f>
         <v/>
       </c>
@@ -29024,10 +29025,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E588" s="2" t="n">
+      <c r="E588" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G588" s="3">
+      <c r="G588" s="5">
         <f>IF(AND(E588&lt;&gt;"",F588&lt;&gt;""),F588-E588,"")</f>
         <v/>
       </c>
@@ -29073,10 +29074,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E589" s="2" t="n">
+      <c r="E589" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G589" s="3">
+      <c r="G589" s="5">
         <f>IF(AND(E589&lt;&gt;"",F589&lt;&gt;""),F589-E589,"")</f>
         <v/>
       </c>
@@ -29122,10 +29123,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E590" s="2" t="n">
+      <c r="E590" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G590" s="3">
+      <c r="G590" s="5">
         <f>IF(AND(E590&lt;&gt;"",F590&lt;&gt;""),F590-E590,"")</f>
         <v/>
       </c>
@@ -29171,10 +29172,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E591" s="2" t="n">
+      <c r="E591" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G591" s="3">
+      <c r="G591" s="5">
         <f>IF(AND(E591&lt;&gt;"",F591&lt;&gt;""),F591-E591,"")</f>
         <v/>
       </c>
@@ -29220,10 +29221,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E592" s="2" t="n">
+      <c r="E592" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G592" s="3">
+      <c r="G592" s="5">
         <f>IF(AND(E592&lt;&gt;"",F592&lt;&gt;""),F592-E592,"")</f>
         <v/>
       </c>
@@ -29269,10 +29270,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E593" s="2" t="n">
+      <c r="E593" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G593" s="3">
+      <c r="G593" s="5">
         <f>IF(AND(E593&lt;&gt;"",F593&lt;&gt;""),F593-E593,"")</f>
         <v/>
       </c>
@@ -29318,10 +29319,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E594" s="2" t="n">
+      <c r="E594" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G594" s="3">
+      <c r="G594" s="5">
         <f>IF(AND(E594&lt;&gt;"",F594&lt;&gt;""),F594-E594,"")</f>
         <v/>
       </c>
@@ -29367,10 +29368,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E595" s="2" t="n">
+      <c r="E595" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G595" s="3">
+      <c r="G595" s="5">
         <f>IF(AND(E595&lt;&gt;"",F595&lt;&gt;""),F595-E595,"")</f>
         <v/>
       </c>
@@ -29416,10 +29417,10 @@
           <t>Service interruption of 16 (2G)(4G) xD and 22 (2G)(4G) xC sites at certain parts of Gua Musang area, Kelantan</t>
         </is>
       </c>
-      <c r="E596" s="2" t="n">
+      <c r="E596" s="4" t="n">
         <v>46226.01527777778</v>
       </c>
-      <c r="G596" s="3">
+      <c r="G596" s="5">
         <f>IF(AND(E596&lt;&gt;"",F596&lt;&gt;""),F596-E596,"")</f>
         <v/>
       </c>
